--- a/workspaces/btc_daily_14days/dxy/dxy_ret_5.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_5.xlsx
@@ -575,46 +575,46 @@
         <v>7</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.62715132317669</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.25368161110634</v>
+        <v>-11.22461893573474</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.645853575238903</v>
+        <v>2.631468214461378</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.77536355267862</v>
+        <v>2.764693967746489</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.236496444504809</v>
+        <v>2.228056325084125</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.533901224461999</v>
+        <v>2.525646893833667</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.450928696866718</v>
+        <v>2.442398557359262</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.984164519234788</v>
+        <v>1.977779057652064</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.927047893497068</v>
+        <v>1.917404721753492</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.072596600479613</v>
+        <v>1.068361063720914</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.45388639131323</v>
+        <v>-13.41310270086827</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.42054746693152</v>
+        <v>-13.37845848528191</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4776457145795447</v>
+        <v>0.478817812799214</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-13.60168368861702</v>
+        <v>-13.55740956028337</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-29.41651524328777</v>
+        <v>-29.33423854562696</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.43906876231862</v>
+        <v>7.410972977161165</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.349888614227268</v>
+        <v>-8.330617972708126</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.220387788946908</v>
+        <v>-8.19735561079559</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.759260388415356</v>
+        <v>-8.733971288283513</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-16.15890040104114</v>
+        <v>-16.10974001073878</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-16.25336866359121</v>
+        <v>-16.20445210524512</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-16.73165929803354</v>
+        <v>-16.68053619970376</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-16.80027386245295</v>
+        <v>-16.75241319090967</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-17.65477853126144</v>
+        <v>-17.60144350499377</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-17.86073998903406</v>
+        <v>-17.80589479594518</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-17.82741394846497</v>
+        <v>-17.7712473594072</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.53849346538338</v>
+        <v>-10.50341112847301</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-10.295351975913</v>
+        <v>-10.26070626357757</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.617672790901764</v>
+        <v>8.583197551697282</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.011560703238302</v>
+        <v>6.984253076733722</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>23.29365973052829</v>
+        <v>23.21484676791781</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.30511642313032</v>
+        <v>12.26473010499291</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.910809306007025</v>
+        <v>-4.897006387149993</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.504585560006618</v>
+        <v>6.484179392929924</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.424049830202073</v>
+        <v>6.403351777994082</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>11.52562881668842</v>
+        <v>11.48981873236344</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.905076295506042</v>
+        <v>5.883215081567961</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.61990538451612</v>
+        <v>10.58629577247545</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.844502111448143</v>
+        <v>4.829760490899446</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.44722616022868</v>
+        <v>10.41650286983196</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.02497036627685</v>
+        <v>9.996748554638963</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.707925657821455</v>
+        <v>4.696558693687138</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>20</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.493732402220985</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.106425296365551</v>
+        <v>-4.099358480406678</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.50125474287313</v>
+        <v>-4.494384227357045</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.634439838023305</v>
+        <v>5.614103112095293</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-9.914028033738589</v>
+        <v>-9.88413147622083</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-9.616586096022928</v>
+        <v>-9.586689538505169</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3054260302389906</v>
+        <v>0.3035097001589762</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1626183613919423</v>
+        <v>-0.1624609266954806</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.804211638253697</v>
+        <v>9.769542356990975</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>13.96230698414074</v>
+        <v>13.91736203923487</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.730866490432454</v>
+        <v>3.719280507264976</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.76430385323377</v>
+        <v>3.753900113247283</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.342000020775473</v>
+        <v>3.334157807679738</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>8.609378635888334</v>
+        <v>8.58544758257483</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>25</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-12.49343832020952</v>
+        <v>-12.46173063121626</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-10.11030973028374</v>
+        <v>-10.08382074474076</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-18.51026296493694</v>
+        <v>-18.45835133910816</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-14.37825520968311</v>
+        <v>-14.33511669708917</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-26.92509085822172</v>
+        <v>-26.83988017828921</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.614836620699378</v>
+        <v>-6.593687439805279</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.698398012104029</v>
+        <v>-2.690754236321958</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8393032224851709</v>
+        <v>0.8362580173869034</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.238632973987613</v>
+        <v>-7.219746489947418</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-12.10340673985418</v>
+        <v>-12.06620952976671</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.30994410302405</v>
+        <v>-12.27051684436996</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-12.27653405778082</v>
+        <v>-12.23589040899978</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-16.70916665465938</v>
+        <v>-16.65305052346138</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-12.45736709474659</v>
+        <v>-12.41455241742415</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>31</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-7.332147997629697</v>
+        <v>-7.316136468681648</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7352901648096619</v>
+        <v>0.7273280619877198</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.887535233891398</v>
+        <v>-2.884746134259203</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.985992458080759</v>
+        <v>-5.968683832523624</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.06946330494563568</v>
+        <v>-0.06884200430143039</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.227641659610455</v>
+        <v>-6.206983413188865</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.316139058074754</v>
+        <v>-6.296400731884638</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.02061968146639</v>
+        <v>-9.988309509010691</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.851693207454574</v>
+        <v>2.838317125981881</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.23739620867056</v>
+        <v>-1.234325065787147</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.443998998282552</v>
+        <v>-1.438616023782494</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.410624640188757</v>
+        <v>-1.403980666624342</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.833233116053883</v>
+        <v>-1.823646811338818</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.584715132626101</v>
+        <v>-1.575842740005982</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>31</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-10.55795444924223</v>
+        <v>-10.53052842225789</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.720560819021692</v>
+        <v>-5.707332518814106</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.796316965858423</v>
+        <v>6.766941840941321</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>13.3816149052005</v>
+        <v>13.33508026273659</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>9.614406827230155</v>
+        <v>9.582774241194073</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>13.13993799499899</v>
+        <v>13.09689151675826</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.603987243118752</v>
+        <v>6.581474332454142</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>9.372203382061606</v>
+        <v>9.341206298100538</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9.320999897614804</v>
+        <v>9.285506582473992</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>11.70022837755278</v>
+        <v>11.66030104572008</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.49354893897767</v>
+        <v>11.45602924996724</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>11.5268814885473</v>
+        <v>11.49067505925709</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>11.10417545945752</v>
+        <v>11.07103330284914</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.36129732311784</v>
+        <v>11.32738306644673</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>46</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.49229205702806</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.770358245386539</v>
+        <v>6.741333439537961</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.375581364173229</v>
+        <v>6.346097431409532</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.505008068333275</v>
+        <v>6.479656277805596</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.965668599431119</v>
+        <v>5.944908078053857</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.613751803887808</v>
+        <v>-4.598026707046429</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.524501785387891</v>
+        <v>-2.516815967702421</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>7.897494797416364</v>
+        <v>7.869927402215687</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.306064360346994</v>
+        <v>1.296253089511538</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.810596071470272</v>
+        <v>4.792246289142135</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2439942596315845</v>
+        <v>0.2431724780088089</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.637091108259384</v>
+        <v>4.622659821229419</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.21425490041225</v>
+        <v>4.203050609509525</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.648429549149192</v>
+        <v>6.628925843444968</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>56</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.27915260592426</v>
+        <v>-4.271536034964598</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.89355631388451</v>
+        <v>-5.879405838903736</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.501333955572292</v>
+        <v>-4.494067376564544</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7979825218801366</v>
+        <v>-0.7990645911517689</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.911374105849326</v>
+        <v>-4.894747187780368</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.826988898052051</v>
+        <v>-2.816506901819736</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.913481330313537</v>
+        <v>-2.903843544724857</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.564502642908643</v>
+        <v>5.543267927581077</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.302053811819654</v>
+        <v>7.270081813600548</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>10.02845999627782</v>
+        <v>9.990109500486454</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.03029578363514</v>
+        <v>8.001566041107353</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.854725657733141</v>
+        <v>9.820580376407591</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.431700552551568</v>
+        <v>9.401018389021409</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>15.06504808929922</v>
+        <v>15.01401901114683</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>76</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8.03287746926371</v>
+        <v>7.994688621910896</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.789987504357704</v>
+        <v>-2.786162280019859</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.551122589224434</v>
+        <v>-0.5580707366934945</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.055307518541696</v>
+        <v>-3.047960093229065</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.9613498045663036</v>
+        <v>-0.958002287648327</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.286448721061006</v>
+        <v>3.274855403682956</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.066720566958999</v>
+        <v>-2.059323035620949</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.535312790306321</v>
+        <v>-2.528033061804436</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.365593010654109</v>
+        <v>1.352881224417793</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.088671080409149</v>
+        <v>-6.06989344462766</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.656906838885781</v>
+        <v>-3.644302476194767</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.942959581652865</v>
+        <v>-4.92454718592677</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.686044921621303</v>
+        <v>-6.658830956720756</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.156623021872718</v>
+        <v>-1.151394522687752</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>93</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.270002540005073</v>
+        <v>1.254076068114692</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.811840683062599</v>
+        <v>1.797470074996831</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7350086844075534</v>
+        <v>-0.7421641601488673</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.682009607526346</v>
+        <v>-1.679238890657679</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06937483876615858</v>
+        <v>-0.06919586901619112</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.924036852196039</v>
+        <v>-1.916026298760976</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.010442782585564</v>
+        <v>-2.002256973074729</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.479183304111928</v>
+        <v>-2.471130893196936</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-6.851603517351158</v>
+        <v>-6.832632886365261</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.000105724671229</v>
+        <v>1.988557515392841</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.792379435750377</v>
+        <v>1.784547432225779</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.062111302064096</v>
+        <v>5.04235147684556</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.716920384421677</v>
+        <v>5.697416964080517</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.974101781201732</v>
+        <v>5.951038980424862</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.50656167979016</v>
+        <v>2.631653651370392</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>8.404032262083867</v>
+        <v>8.642659875433523</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.507198659733263</v>
+        <v>5.693983254339486</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.636104029910179</v>
+        <v>5.787328431154357</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.347494837445986</v>
+        <v>6.493759527511003</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>14.15154081107192</v>
+        <v>14.47205044861016</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>12.82671838965721</v>
+        <v>13.11772607300652</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>11.79376927361943</v>
+        <v>12.07263089444026</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>13.63810459607067</v>
+        <v>13.99343287720539</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>11.57384048607427</v>
+        <v>11.86379756474099</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>15.14845036300942</v>
+        <v>15.50269890435486</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>8.923837559284806</v>
+        <v>9.132485537287806</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>12.28675021699113</v>
+        <v>12.55602793143016</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>13.77901835730756</v>
+        <v>14.09826809539577</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>88</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-9.311620138392051</v>
+        <v>-9.294679395979109</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.10632677112045</v>
+        <v>-4.102382257281789</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.638548977875587</v>
+        <v>-5.63163487265259</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.372421537799141</v>
+        <v>-4.364039445891819</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.912374296991139</v>
+        <v>1.905650693856977</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.339351233811804</v>
+        <v>-2.334936067753809</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.425812743367338</v>
+        <v>-2.421013471913653</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.754486398823403</v>
+        <v>-1.752906287812479</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.950867614346421</v>
+        <v>-2.950760963869627</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3889212901176293</v>
+        <v>-0.3932855398897956</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5951564947435273</v>
+        <v>-0.5972979240530236</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5767484857219642</v>
+        <v>0.5728697762780257</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.431702174384355</v>
+        <v>2.42410192462026</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.150473920282458</v>
+        <v>-4.141825144697073</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.616245337753689</v>
+        <v>-1.608135109288902</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.862848024859368</v>
+        <v>-5.884800601405615</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9889952448643058</v>
+        <v>-0.9755476219090298</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-11.39798013111412</v>
+        <v>-11.46675448096342</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.912536336420317</v>
+        <v>-4.941090270923901</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.736674976660467</v>
+        <v>-3.757425282280245</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-6.462132889329006</v>
+        <v>-6.501602879891315</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.17101748791513</v>
+        <v>-5.198039121979676</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.10746956558765</v>
+        <v>-6.128953019543708</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-6.082142559125359</v>
+        <v>-6.109164193189905</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.167744001008941</v>
+        <v>-7.206394140135323</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.376261138151783</v>
+        <v>-5.406277739707022</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.16116596449978</v>
+        <v>-3.179185964430111</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.300660778013189</v>
+        <v>-3.317207284681331</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>118</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-10.96801459139647</v>
+        <v>-10.94871569760372</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.501234445178874</v>
+        <v>-7.488450438118839</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.501412643324947</v>
+        <v>-4.498348636216505</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.374989519603275</v>
+        <v>-4.364265494723519</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.519869228890656</v>
+        <v>-1.516567198631122</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-6.312803383333467</v>
+        <v>-6.29824069418067</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.857477450701793</v>
+        <v>-3.847882874673466</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.775371805615023</v>
+        <v>-1.772693392099029</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.5310353703522</v>
+        <v>-3.528608532518575</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1379755725397942</v>
+        <v>-0.1414455819533345</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3452880287999349</v>
+        <v>-0.3461989062709137</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.387341591819812</v>
+        <v>1.383099505311812</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.7334627011475163</v>
+        <v>-0.7320703598703844</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.030727193991247</v>
+        <v>-3.024721908950021</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>95</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.282912004420503</v>
+        <v>-8.26532910626279</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.68873524196853</v>
+        <v>1.680188260104117</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.920756365475249</v>
+        <v>-2.92111017722447</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.420824362471706</v>
+        <v>1.418867991622776</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.990703189475262</v>
+        <v>2.982673050264218</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.395950873440668</v>
+        <v>5.382835557519662</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.317280004217508</v>
+        <v>5.30465949820789</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6300483978156208</v>
+        <v>0.6269497836369098</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.796034693761619</v>
+        <v>4.776476213244088</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>9.219483059436058</v>
+        <v>9.189508922953067</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.733887830169799</v>
+        <v>3.721597703898581</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.878955850802242</v>
+        <v>5.861244019138752</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8.62258106648806</v>
+        <v>8.598884145036017</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>8.873293537979706</v>
+        <v>8.848605477312248</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>98</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.473030156944667</v>
+        <v>-1.471526290784496</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.001518674686096</v>
+        <v>0.9925390916185037</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.629954134585432</v>
+        <v>1.615182545056761</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.311423980616254</v>
+        <v>-1.305382054118432</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.260874861205664</v>
+        <v>3.249558306568247</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5297436220974845</v>
+        <v>-0.52820464081978</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.663169615130613</v>
+        <v>-2.654524175261493</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.129491108411386</v>
+        <v>-3.121707574042993</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5.229557125260627</v>
+        <v>-5.223523786755912</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.106326096002739</v>
+        <v>-7.094057135049205</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.199408129266828</v>
+        <v>-2.196769643040192</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.164594019170998</v>
+        <v>-2.162386485694761</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.587003393867626</v>
+        <v>-2.582641096639726</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2887349704168471</v>
+        <v>-0.2921034378327718</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.942205244146457</v>
+        <v>3.98165719498428</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.580239310817738</v>
+        <v>-7.623122169394712</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-9.956949924510575</v>
+        <v>-10.00696725394414</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.891577198372396</v>
+        <v>-2.922383412675224</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.403498541480893</v>
+        <v>-6.448206202550523</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.11528310369556</v>
+        <v>-5.157063477433184</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.637362407523582</v>
+        <v>-6.695340501792167</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-8.099037379660551</v>
+        <v>-8.162523900573667</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.197707796444604</v>
+        <v>-6.223523786755912</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.037679199639143</v>
+        <v>-7.07364897178384</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.229740296665021</v>
+        <v>-7.278402296101476</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.20467323415172</v>
+        <v>-6.244019138756045</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-7.610534859347801</v>
+        <v>-7.664273749700889</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-8.359112768614452</v>
+        <v>-8.414552417424659</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>109</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.952153916540276</v>
+        <v>-2.949541425451486</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.8126466827756</v>
+        <v>-1.811433951522858</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-10.48162094954278</v>
+        <v>-10.46318339206434</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.923932602049433</v>
+        <v>-3.910911910833015</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.620970980098512</v>
+        <v>-2.614470740584061</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-4.16403062802901</v>
+        <v>-4.151891188189559</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-4.250967473743614</v>
+        <v>-4.236624905461781</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.958940683965622</v>
+        <v>-1.951514726261635</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.770338244937932</v>
+        <v>-4.764808190425605</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.865218872602682</v>
+        <v>-2.862639797471942</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.523570817646728</v>
+        <v>1.519762841513312</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.199934336501933</v>
+        <v>-1.198147579122931</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.54242255586805</v>
+        <v>-2.535833382728384</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4678308420331803</v>
+        <v>0.4661815275295496</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>96</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.451771653543275</v>
+        <v>-1.452082864241824</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.024286025789948</v>
+        <v>-2.021678599840897</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.757315855848745</v>
+        <v>1.750119360229178</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9.190671080356793</v>
+        <v>9.172039159503321</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.477924816116015</v>
+        <v>4.466951277764508</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.682125201891786</v>
+        <v>2.681059882146833</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>11.99731102690446</v>
+        <v>11.97132616487455</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.174325732896833</v>
+        <v>3.170809432759725</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.009729758506303199</v>
+        <v>-0.01519045342261194</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.1814019847690247</v>
+        <v>0.176351028216196</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.152404068997804</v>
+        <v>4.138264370565246</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.14123921990663</v>
+        <v>3.130980861244048</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.850476831382586</v>
+        <v>5.835726250299075</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.925873114490329</v>
+        <v>1.918780915908755</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>68</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.022850084915859</v>
+        <v>-1.024993204481575</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-10.02213055367213</v>
+        <v>-9.987364874350703</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-7.464553914314237</v>
+        <v>-7.441057110359061</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.391171952772403</v>
+        <v>-4.369627507163365</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.878544819916428</v>
+        <v>-7.849225192823731</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.160586815661702</v>
+        <v>-3.140018549225715</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.240662274423897</v>
+        <v>-3.224752266497994</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.188726604692675</v>
+        <v>-5.162523900573568</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.710809823694554</v>
+        <v>-6.694112022050028</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-7.565593267232558</v>
+        <v>-7.544237207077956</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-9.247733829154825</v>
+        <v>-9.219578766689658</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-7.739457128087167</v>
+        <v>-7.714607374050104</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-8.164369997542181</v>
+        <v>-8.134861984995005</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-6.43493229840611</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>63</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.1206145503245324</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>1.450543622381325</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.131091489372494</v>
+        <v>-2.118928258818435</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.178187810766985</v>
+        <v>1.185928048392277</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.6417016551010875</v>
+        <v>0.6475068333200653</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6639149067934511</v>
+        <v>-0.6423528162658627</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.931544910410324</v>
+        <v>-3.901689708141319</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.813085344238537</v>
+        <v>-2.781571519621274</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.232137565484614</v>
+        <v>-9.191777755009852</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.304048202183054</v>
+        <v>-5.279998178133049</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8.703308169283169</v>
+        <v>-8.659354677053805</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-5.480223547374202</v>
+        <v>-5.450368345105197</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.312900133959417</v>
+        <v>-4.283321368748503</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.055438564057859</v>
+        <v>-4.033600036472194</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>49</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.690235149177781</v>
+        <v>6.630685701257889</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>13.32106364246993</v>
+        <v>13.24192684233596</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>17.03522109667324</v>
+        <v>16.92869078880058</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>21.26094198726044</v>
+        <v>21.14057657446933</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>22.78042345329327</v>
+        <v>22.64297168592775</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>27.16994354828361</v>
+        <v>27.02204627670466</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14.76491055002175</v>
+        <v>14.6924146002487</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>14.28416874842011</v>
+        <v>14.2252312014672</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.14125950707815</v>
+        <v>10.08259866222365</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>13.39677088214512</v>
+        <v>13.31410613025697</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.069432994207489</v>
+        <v>9.027720152878175</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.16171883265791</v>
+        <v>11.10291963675421</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.622269258797964</v>
+        <v>6.601032372748094</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.99457515469432</v>
+        <v>10.93238635808558</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-9.636295463067121</v>
+        <v>-9.74547084053517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-10.01744402010296</v>
+        <v>-10.20257290878398</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-15.2061765809661</v>
+        <v>-15.47549039586835</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.901107213139696</v>
+        <v>-8.028164092529195</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.090535139621267</v>
+        <v>-6.127560917357428</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.397702579494222</v>
+        <v>1.486954191089907</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.765970095911634</v>
+        <v>-5.91485269691406</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9736218328875879</v>
+        <v>0.9350370750361492</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.564207711332458</v>
+        <v>-1.564987201390075</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-9.573169585398396</v>
+        <v>-9.732185557149691</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.920140870725866</v>
+        <v>-5.058890100979454</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-9.67962156764699</v>
+        <v>-9.902555724121825</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.258073685782662</v>
+        <v>-5.444761554578939</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.104229630591732</v>
+        <v>-5.195040222302637</v>
       </c>
     </row>
     <row r="30">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.01568</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1640~1645</t>
-        </is>
+      <c r="B6" t="n">
+        <v>1640</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-2.645414004100552</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.01462</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1633~1638</t>
-        </is>
+      <c r="B7" t="n">
+        <v>1633</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-2.676588503360158</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.01355</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1620~1625</t>
-        </is>
+      <c r="B8" t="n">
+        <v>1620</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-2.462669089440737</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.01248</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1602~1607</t>
-        </is>
+      <c r="B9" t="n">
+        <v>1602</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-2.586779950577117</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.01141</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1582~1587</t>
-        </is>
+      <c r="B10" t="n">
+        <v>1582</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-2.587956278622073</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.01034</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1557~1562</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1557</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-2.429417833654284</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.009271</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1526~1531</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1526</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-2.330146354174701</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.008203</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1495~1500</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1495</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-2.160104986876647</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.007134</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1449~1454</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1449</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-2.149559365601995</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.006065</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1393~1398</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1393</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-2.064253770853753</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.004996</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1317~1322</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1317</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-2.644724250618452</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.003927</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1224~1229</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1224</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-2.940956627777105</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.002858</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1146~1149</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1146</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-3.32024423839971</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.00179</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1058~1061</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1058</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-2.823315794291027</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.0007207</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>945~947</t>
-        </is>
+      <c r="B20" t="n">
+        <v>945</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-2.96862311429657</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.0003481</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>827~829</t>
-        </is>
+      <c r="B21" t="n">
+        <v>827</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.829988380523609</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.001417</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>732~734</t>
-        </is>
+      <c r="B22" t="n">
+        <v>732</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.9948007180301346</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.002486</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>634~636</t>
-        </is>
+      <c r="B23" t="n">
+        <v>634</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.921111276184817</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.003555</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>534~535</t>
-        </is>
+      <c r="B24" t="n">
+        <v>534</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.839232712733342</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.004623</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>425~426</t>
-        </is>
+      <c r="B25" t="n">
+        <v>425</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.554471184059736</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.005692</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>329~330</t>
-        </is>
+      <c r="B26" t="n">
+        <v>329</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.584347411119069</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.006761</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>261~262</t>
-        </is>
+      <c r="B27" t="n">
+        <v>261</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.730079541584018</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.00783</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>198~199</t>
-        </is>
+      <c r="B28" t="n">
+        <v>198</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-2.242182038802945</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.008899</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>149~150</t>
-        </is>
+      <c r="B29" t="n">
+        <v>149</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-5.16010498687664</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.009968</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>108~108</t>
-        </is>
+      <c r="B30" t="n">
+        <v>108</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-3.419364246135899</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.01104</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B31" t="n">
+        <v>84</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.01211</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>67~67</t>
-        </is>
+      <c r="B32" t="n">
+        <v>67</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>5.715516903670625</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.01317</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>54~54</t>
-        </is>
+      <c r="B33" t="n">
+        <v>54</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>4.91396908719743</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.01424</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>43~43</t>
-        </is>
+      <c r="B34" t="n">
+        <v>43</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>7.971677958859786</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.01531</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>34~34</t>
-        </is>
+      <c r="B35" t="n">
+        <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>9.271267562142967</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.01568</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>34~34</t>
-        </is>
+      <c r="B6" t="n">
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>12.2124440327312</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.01462</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>41~41</t>
-        </is>
+      <c r="B7" t="n">
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10.92119582613149</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.01355</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>54~54</t>
-        </is>
+      <c r="B8" t="n">
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.210265383493734</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.01248</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>72~72</t>
-        </is>
+      <c r="B9" t="n">
+        <v>72</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3.062117235345582</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.01141</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>92~92</t>
-        </is>
+      <c r="B10" t="n">
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.854387766746541</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.01034</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>117~117</t>
-        </is>
+      <c r="B11" t="n">
+        <v>117</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.211387038158698</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.009271</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>148~148</t>
-        </is>
+      <c r="B12" t="n">
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.008203</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>179~179</t>
-        </is>
+      <c r="B13" t="n">
+        <v>179</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-3.890086364902714</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.007134</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>225~225</t>
-        </is>
+      <c r="B14" t="n">
+        <v>225</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-3.60454943132109</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.006065</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>281~281</t>
-        </is>
+      <c r="B15" t="n">
+        <v>281</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-3.738989921633461</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.004996</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>357~357</t>
-        </is>
+      <c r="B16" t="n">
+        <v>357</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.232934118529307</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.003927</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>450~450</t>
-        </is>
+      <c r="B17" t="n">
+        <v>450</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.7156605424321967</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.002858</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>528~530</t>
-        </is>
+      <c r="B18" t="n">
+        <v>528</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.2292873768137511</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.00179</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>616~618</t>
-        </is>
+      <c r="B19" t="n">
+        <v>616</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.52256453380221</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.0007207</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>729~732</t>
-        </is>
+      <c r="B20" t="n">
+        <v>729</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.537154167204513</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.0003481</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>847~850</t>
-        </is>
+      <c r="B21" t="n">
+        <v>847</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-2.846379496680562</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.001417</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>942~945</t>
-        </is>
+      <c r="B22" t="n">
+        <v>942</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-3.392909219680874</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.002486</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1040~1043</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1040</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-3.212517898349958</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.003555</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1140~1144</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1140</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-2.580850907622562</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.004623</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1249~1253</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1249</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-2.613151009755072</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.005692</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1345~1349</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1345</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-2.530502812426427</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.006761</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1413~1417</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1413</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-2.458152505107648</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.00783</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1476~1480</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1476</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-2.358303185074838</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.008899</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1525~1529</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1525</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-2.068323866318543</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.009968</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1566~1571</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1566</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-2.270650287110037</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.01104</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1590~1595</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1590</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-2.462090357827535</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.01211</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1607~1612</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1607</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-2.679542538572257</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.01317</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1620~1625</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1620</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-2.585746012517667</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.01424</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1631~1636</t>
-        </is>
+      <c r="B34" t="n">
+        <v>1631</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-2.61568770896303</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.01531</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1640~1645</t>
-        </is>
+      <c r="B35" t="n">
+        <v>1640</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-2.584623730544322</v>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_5.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_5.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-5 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-5 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,1509 +568,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01515</t>
+          <t>X ≈ -0.01675</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.62715132317669</v>
+        <v>2.350905368229192</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.22461893573474</v>
+        <v>3.961469771917962</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.631468214461378</v>
+        <v>0.3510194161962801</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.764693967746489</v>
+        <v>-2.736585377903232</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.228056325084125</v>
+        <v>3.162640040231558</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.525646893833667</v>
+        <v>3.460233554306321</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.442398557359262</v>
+        <v>3.376594767358654</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.977779057652064</v>
+        <v>2.910856159521501</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.917404721753492</v>
+        <v>2.850729441507369</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.068361063720914</v>
+        <v>-7.665556054184421</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.41310270086827</v>
+        <v>-7.872053171723074</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.37845848528191</v>
+        <v>-1.391152172127306</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.478817812799214</v>
+        <v>-5.036543299196673</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-13.55740956028337</v>
+        <v>-11.26369173054358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01409</t>
+          <t>X ≈ -0.01554</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-29.33423854562696</v>
+        <v>14.14074095267141</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.410972977161165</v>
+        <v>12.53793132315532</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.330617972708126</v>
+        <v>8.453151435583926</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.19735561079559</v>
+        <v>12.28002825640717</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.733971288283513</v>
+        <v>15.44098064244107</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-16.10974001073878</v>
+        <v>15.74161725398754</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-16.20445210524512</v>
+        <v>15.66103531074833</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-16.68053619970376</v>
+        <v>22.59475690650176</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-16.75241319090967</v>
+        <v>15.14128882498788</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-17.60144350499377</v>
+        <v>17.99606619481996</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-17.80589479594518</v>
+        <v>14.09495525154384</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-17.7712473594072</v>
+        <v>17.83468337782008</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.50341112847301</v>
+        <v>13.71628998157871</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-10.26070626357757</v>
+        <v>13.9453883172493</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01301</t>
+          <t>X ≈ -0.01434</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.583197551697282</v>
+        <v>3.322502803989117</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.984253076733722</v>
+        <v>6.354344505373128</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>23.21484676791781</v>
+        <v>10.60014292660565</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.26473010499291</v>
+        <v>10.73299347911266</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.897006387149993</v>
+        <v>10.19811656100224</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.484179392929924</v>
+        <v>1.213795989879607</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.403351777994082</v>
+        <v>1.129649883399097</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>11.48981873236344</v>
+        <v>2.985425379186637</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.883215081567961</v>
+        <v>2.925439870420902</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.58629577247545</v>
+        <v>11.37018659687807</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.829760490899446</v>
+        <v>8.844629765462329</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.41650286983196</v>
+        <v>8.88122369200412</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.996748554638963</v>
+        <v>6.138458419925925</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.696558693687138</v>
+        <v>4.040134225947007</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01195</t>
+          <t>X ≈ -0.01312</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.493732402220985</v>
+        <v>6.321923095872158</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.099358480406678</v>
+        <v>10.58177957392778</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.494384227357045</v>
+        <v>12.14551407182524</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.614103112095293</v>
+        <v>18.14626826988506</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-9.88413147622083</v>
+        <v>5.875478276165545</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-9.586689538505169</v>
+        <v>14.00124740349555</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3035097001589762</v>
+        <v>8.048444340058914</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1624609266954806</v>
+        <v>5.626066068610236</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.769542356990975</v>
+        <v>5.566774199006318</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>13.91736203923487</v>
+        <v>8.636712795838065</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.719280507264976</v>
+        <v>2.556511590858243</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.753900113247283</v>
+        <v>10.43071697643807</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.334157807679738</v>
+        <v>8.053120444692112</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>8.58544758257483</v>
+        <v>4.359331672367439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01087</t>
+          <t>X ≈ -0.01192</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-12.46173063121626</v>
+        <v>-4.923503711262072</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-10.08382074474076</v>
+        <v>-6.531062919485606</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-18.45835133910816</v>
+        <v>-5.292327049352707</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-14.33511669708917</v>
+        <v>-11.70411931528068</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-26.83988017828921</v>
+        <v>-10.60866607024776</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.593687439805279</v>
+        <v>-5.406645702956475</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.690754236321958</v>
+        <v>2.689657866809291</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8362580173869034</v>
+        <v>2.223810862326523</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.219746489947418</v>
+        <v>0.5264588783904003</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-12.06620952976671</v>
+        <v>1.315177471894678</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.27051684436996</v>
+        <v>-3.803138992974233</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-12.23589040899978</v>
+        <v>-3.769761449842534</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-16.65305052346138</v>
+        <v>-0.9128028693784387</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-12.41455241742415</v>
+        <v>2.591411389500195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.009805</t>
+          <t>X ≈ -0.0107</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-7.316136468681648</v>
+        <v>-0.580018426074183</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7273280619877198</v>
+        <v>-5.971808690377728</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.884746134259203</v>
+        <v>-8.892081832478979</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.968683832523624</v>
+        <v>-6.239106701938759</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.06884200430143039</v>
+        <v>-11.82920937177793</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.206983413188865</v>
+        <v>-3.956726574643987</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.296400731884638</v>
+        <v>-2.778764440253774</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.988309509010691</v>
+        <v>-1.982178701869309</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.838317125981881</v>
+        <v>-2.043339051073602</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.234325065787147</v>
+        <v>-1.628450978506621</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.438616023782494</v>
+        <v>-1.833229203746704</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.403980666624342</v>
+        <v>-3.064526388023623</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.823646811338818</v>
+        <v>-4.750755084927093</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.575842740005982</v>
+        <v>-3.260425091097446</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.008737</t>
+          <t>X ≈ -0.009495</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-10.53052842225789</v>
+        <v>1.631245847375538</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.707332518814106</v>
+        <v>-1.146655937219563</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.766941840941321</v>
+        <v>4.323776053647052</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>13.33508026273659</v>
+        <v>3.281756505082178</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>9.582774241194073</v>
+        <v>1.572137883678138</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>13.09689151675826</v>
+        <v>-0.4791355410908835</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.581474332454142</v>
+        <v>1.784694948537762</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>9.341206298100538</v>
+        <v>4.842348501533365</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9.285506582473992</v>
+        <v>9.482568458416054</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>11.66030104572008</v>
+        <v>5.110440559372606</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.45602924996724</v>
+        <v>3.731952355404921</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>11.49067505925709</v>
+        <v>3.767301250900225</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>11.07103330284914</v>
+        <v>2.172229395279345</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.32738306644673</v>
+        <v>2.398547358641956</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.007668</t>
+          <t>X ≈ -0.008286</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.49229205702806</v>
+        <v>-3.727826935735472</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.741333439537961</v>
+        <v>-1.983953221289468</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.346097431409532</v>
+        <v>-2.379123318741833</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.479656277805596</v>
+        <v>1.940460425065815</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.944908078053857</v>
+        <v>1.404291664159842</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.598026707046429</v>
+        <v>3.377867220875714</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.516815967702421</v>
+        <v>1.616749440140723</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>7.869927402215687</v>
+        <v>0.3116275502234274</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.296253089511538</v>
+        <v>0.2509801408088421</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.792246289142135</v>
+        <v>4.43859108298679</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2431724780088089</v>
+        <v>1.716652162514542</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.622659821229419</v>
+        <v>0.9116269273608566</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.203050609509525</v>
+        <v>3.852400978558279</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.628925843444968</v>
+        <v>4.079219627549513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.006599</t>
+          <t>X ≈ -0.007076</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.271536034964598</v>
+        <v>-4.749966876461855</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.879405838903736</v>
+        <v>-1.14596242392011</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.494067376564544</v>
+        <v>-2.192432571250492</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7990645911517689</v>
+        <v>-2.063268081197435</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.894747187780368</v>
+        <v>-0.6447626854825899</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.816506901819736</v>
+        <v>-4.913455050075264</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.903843544724857</v>
+        <v>-1.73804501339395</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.543267927581077</v>
+        <v>1.709653332360027</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.270081813600548</v>
+        <v>0.996792008264535</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>9.990109500486454</v>
+        <v>0.1481043192536475</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.001566041107353</v>
+        <v>2.556129989975261</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.820580376407591</v>
+        <v>6.510560177816217</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.401018389021409</v>
+        <v>4.785750839523736</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>15.01401901114683</v>
+        <v>7.627305528576748</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.00553</t>
+          <t>X ≈ -0.005867</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7.994688621910896</v>
+        <v>0.3762085836836775</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.786162280019859</v>
+        <v>-5.0245524375011</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5580707366934945</v>
+        <v>-3.522333376369794</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.047960093229065</v>
+        <v>-4.817860439503498</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.958002287648327</v>
+        <v>-3.931386643316117</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.274855403682956</v>
+        <v>-0.3111166752632357</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.059323035620949</v>
+        <v>-3.722197429413697</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.528033061804436</v>
+        <v>-1.813634937543675</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.352881224417793</v>
+        <v>2.404282016515822</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.06989344462766</v>
+        <v>-2.72424573461354</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.644302476194767</v>
+        <v>-3.880744356998356</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.92454718592677</v>
+        <v>-0.5163473984983753</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.658830956720756</v>
+        <v>-0.4602191550467865</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.151394522687752</v>
+        <v>1.670256042115234</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.004462</t>
+          <t>X ≈ -0.004657</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>93</v>
+        <v>241</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.254076068114692</v>
+        <v>6.413964902649681</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.797470074996831</v>
+        <v>1.919554641181257</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7421641601488673</v>
+        <v>-0.1285229659639739</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.679238890657679</v>
+        <v>-0.8257948259787184</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06919586901619112</v>
+        <v>1.532999637467888</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.916026298760976</v>
+        <v>-1.481554523075793</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.002256973074729</v>
+        <v>0.5034087795175708</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.471130893196936</v>
+        <v>-4.518773146407817</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-6.832632886365261</v>
+        <v>-4.581343427550166</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.988557515392841</v>
+        <v>-2.530465359305303</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.784547432225779</v>
+        <v>-1.491820101939638</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.04235147684556</v>
+        <v>-3.94619045764022</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.697416964080517</v>
+        <v>-3.952428182703173</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.951038980424862</v>
+        <v>-2.06813558009361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.003392</t>
+          <t>X ≈ -0.003448</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.631653651370392</v>
+        <v>6.107308031836148</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>8.642659875433523</v>
+        <v>8.775086332866714</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.693983254339486</v>
+        <v>6.463031303477784</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.787328431154357</v>
+        <v>3.717314622759631</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.493759527511003</v>
+        <v>4.133896042386951</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>14.47205044861016</v>
+        <v>7.320519722706649</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>13.11772607300652</v>
+        <v>7.238668419654303</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>12.07263089444026</v>
+        <v>5.807448087411785</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>13.99343287720539</v>
+        <v>4.571583349643568</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>11.86379756474099</v>
+        <v>6.379239975633624</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>15.50269890435486</v>
+        <v>5.692446684293451</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>9.132485537287806</v>
+        <v>5.998551413619793</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>12.55602793143016</v>
+        <v>8.25012749355686</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>14.09826809539577</v>
+        <v>7.036556408415592</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002324</t>
+          <t>X ≈ -0.002238</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88</v>
+        <v>255</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-9.294679395979109</v>
+        <v>-6.782451579703263</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.102382257281789</v>
+        <v>-5.269990147882339</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.63163487265259</v>
+        <v>-3.711113307287107</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.364039445891819</v>
+        <v>-3.191299788860078</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.905650693856977</v>
+        <v>-0.9908808136594658</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.334936067753809</v>
+        <v>-1.083761612116795</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.421013471913653</v>
+        <v>-2.344225103783494</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.752906287812479</v>
+        <v>-2.421477298286341</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.950760963869627</v>
+        <v>-3.266209534071834</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3932855398897956</v>
+        <v>-6.078922710961429</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5972979240530236</v>
+        <v>-4.326855604158837</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5728697762780257</v>
+        <v>-5.467397455750529</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.42410192462026</v>
+        <v>-1.575937251988279</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.141825144697073</v>
+        <v>-3.483805582534515</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001255</t>
+          <t>X ≈ -0.001028</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>113</v>
+        <v>275</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.608135109288902</v>
+        <v>0.4178304671334701</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.884800601405615</v>
+        <v>2.431498516161007</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9755476219090298</v>
+        <v>1.311777262743895</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-11.46675448096342</v>
+        <v>-1.098783092289011</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.941090270923901</v>
+        <v>1.993590831763662</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.757425282280245</v>
+        <v>-0.9760982497576975</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-6.501602879891315</v>
+        <v>-0.3344591356974504</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.198039121979676</v>
+        <v>-1.530319255634318</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.128953019543708</v>
+        <v>-1.227665048520812</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-6.109164193189905</v>
+        <v>-0.9905600653059352</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.206394140135323</v>
+        <v>-0.9922177296639276</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.406277739707022</v>
+        <v>-1.321475940944879</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.179185964430111</v>
+        <v>-1.377990430622013</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.317207284681331</v>
+        <v>-2.243163871304567</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.0001863</t>
+          <t>X ≈ 0.0001812</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>118</v>
+        <v>301</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-10.94871569760372</v>
+        <v>-2.637563843394034</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.488450438118839</v>
+        <v>-1.925870703994633</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.498348636216505</v>
+        <v>-1.989875042422057</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.364265494723519</v>
+        <v>1.455797757861312</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.516567198631122</v>
+        <v>1.580739817646368</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-6.29824069418067</v>
+        <v>-1.108331968198115</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.847882874673466</v>
+        <v>0.1347628591358401</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.772693392099029</v>
+        <v>-1.660970798255121</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.528608532518575</v>
+        <v>-0.7252752139140242</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1414455819533345</v>
+        <v>1.747065125968582</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3461989062709137</v>
+        <v>0.2134603132233437</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.383099505311812</v>
+        <v>0.9122902928211829</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.7320703598703844</v>
+        <v>0.8243653531291173</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.024721908950021</v>
+        <v>-1.939932219235708</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0008826</t>
+          <t>X ≈ 0.00139</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>95</v>
+        <v>252</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.26532910626279</v>
+        <v>-3.259455352103693</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.680188260104117</v>
+        <v>1.460453153531496</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.92111017722447</v>
+        <v>1.066713036428347</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.418867991622776</v>
+        <v>0.8016245575150904</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.982673050264218</v>
+        <v>-1.321996727578622</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.382835557519662</v>
+        <v>0.1639821236219419</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>-0.7138368757557316</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6269497836369098</v>
+        <v>-2.371565113500594</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>-0.4484202858963826</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>9.189508922953067</v>
+        <v>0.2889625050753395</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>-0.3125640500101596</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.861244019138752</v>
+        <v>-0.2781858976549216</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8.598884145036017</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>8.848605477312248</v>
+        <v>0.3210496929089928</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001952</t>
+          <t>X ≈ 0.0026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>98</v>
+        <v>278</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.471526290784496</v>
+        <v>3.263077988955132</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.9925390916185037</v>
+        <v>-0.8490536727631763</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.615182545056761</v>
+        <v>-0.8855808551747444</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.305382054118432</v>
+        <v>-4.342784965459387</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.249558306568247</v>
+        <v>0.8579294755609297</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.52820464081978</v>
+        <v>0.078323101363722</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.654524175261493</v>
+        <v>-0.3657207801877362</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.121707574042993</v>
+        <v>-0.1133716682567893</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-1.253490515427082</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.094057135049205</v>
+        <v>-1.383984851325252</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.196769643040192</v>
+        <v>-1.948398239801278</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.162386485694761</v>
+        <v>-2.633444547877602</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.582641096639726</v>
+        <v>-2.334170940759364</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2921034378327718</v>
+        <v>-2.827859750964528</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00302</t>
+          <t>X ≈ 0.00381</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.98165719498428</v>
+        <v>4.41283940931222</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.623122169394712</v>
+        <v>0.6492651886882896</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-10.00696725394414</v>
+        <v>-3.628800438253876</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.922383412675224</v>
+        <v>-1.77640868136556</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.448206202550523</v>
+        <v>-0.5846235062240268</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.157063477433184</v>
+        <v>-2.882612212631301</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.695340501792167</v>
+        <v>0.06089485176469367</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-8.162523900573667</v>
+        <v>0.69481295287747</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.223523786755912</v>
+        <v>1.499631662155608</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.07364897178384</v>
+        <v>2.814215030327873</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.278402296101476</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.244019138756045</v>
+        <v>1.3451907257217</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-7.664273749700889</v>
+        <v>0.05923900660742731</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-8.414552417424659</v>
+        <v>3.748178120037466</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.004089</t>
+          <t>X ≈ 0.005019</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>109</v>
+        <v>247</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.949541425451486</v>
+        <v>-1.269976096825268</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.811433951522858</v>
+        <v>-1.851490764141921</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-10.46318339206434</v>
+        <v>-1.438642551555226</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.910911910833015</v>
+        <v>5.551664406493884</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.614470740584061</v>
+        <v>-0.6437709304773023</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-4.151891188189559</v>
+        <v>-1.154749090305941</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-4.236624905461781</v>
+        <v>0.7833127970428251</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.951514726261635</v>
+        <v>-0.8983307455293428</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.764808190425605</v>
+        <v>-0.1495963028618803</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.862639797471942</v>
+        <v>-1.404373398786873</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.519762841513312</v>
+        <v>1.224933540118919</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.198147579122931</v>
+        <v>0.04473679368886252</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.535833382728384</v>
+        <v>0.4343025395657421</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4661815275295496</v>
+        <v>-0.9593950085883378</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.005158</t>
+          <t>X ≈ 0.006229</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.452082864241824</v>
+        <v>-1.527056373065328</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.021678599840897</v>
+        <v>-4.054389044702397</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.750119360229178</v>
+        <v>-1.636392063299624</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9.172039159503321</v>
+        <v>-2.454407413127555</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.466951277764508</v>
+        <v>-4.412661875074328</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.681059882146833</v>
+        <v>-3.6482773629874</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>-5.153972360699179</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.170809432759725</v>
+        <v>-4.205946664863333</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.01519045342261194</v>
+        <v>-6.153721274216245</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.176351028216196</v>
+        <v>-7.003640070546105</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.138264370565246</v>
+        <v>-4.378152549561015</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.130980861244048</v>
+        <v>-3.400378170790653</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.835726250299075</v>
+        <v>-5.707321476934247</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.918780915908755</v>
+        <v>-5.481585826707658</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.006226</t>
+          <t>X ≈ 0.007438</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.024993204481575</v>
+        <v>2.746733000237015</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-9.987364874350703</v>
+        <v>3.911111927045901</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-7.441057110359061</v>
+        <v>5.715375457329429</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.369627507163365</v>
+        <v>6.394982237969081</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.849225192823731</v>
+        <v>4.758310741798944</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.140018549225715</v>
+        <v>5.065179744029379</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.224752266497994</v>
+        <v>2.223803100574628</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.162523900573568</v>
+        <v>2.861706832478532</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.694112022050028</v>
+        <v>1.695752300265184</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-7.544237207077956</v>
+        <v>0.8458335039352889</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-9.219578766689658</v>
+        <v>-2.12129859355143</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-7.714607374050104</v>
+        <v>1.227996685875723</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-8.134861984995005</v>
+        <v>0.8078458325623146</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-0.07139089290179612</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.007295</t>
+          <t>X ≈ 0.008648</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1206145503245324</v>
+        <v>5.588342736695139</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>7.096665550375917</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.118928258818435</v>
+        <v>11.31865332799436</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.185928048392277</v>
+        <v>13.00005551980946</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>11.7120928147153</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6423528162658627</v>
+        <v>15.13588059360325</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.901689708141319</v>
+        <v>6.558035830027791</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.781571519621274</v>
+        <v>8.416548581589822</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.191777755009852</v>
+        <v>6.805178828167818</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.279998178133049</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8.659354677053805</v>
+        <v>4.20017127667856</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-5.450368345105197</v>
+        <v>4.234549429033883</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.283321368748503</v>
+        <v>2.264010978821261</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.033600036472194</v>
+        <v>4.815328024396671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.008365</t>
+          <t>X ≈ 0.009857</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.630685701257889</v>
+        <v>-7.273780277222045</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>13.24192684233596</v>
+        <v>-2.158663109665724</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>16.92869078880058</v>
+        <v>-1.081196867018399</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>21.14057657446933</v>
+        <v>-4.820911946669426</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>22.64297168592775</v>
+        <v>-11.16456645467533</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>27.02204627670466</v>
+        <v>-3.142471532730674</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14.6924146002487</v>
+        <v>-7.109458713511053</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>14.2252312014672</v>
+        <v>-2.722158425258925</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.08259866222365</v>
+        <v>-3.754014368189523</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>13.31410613025697</v>
+        <v>-6.545680737334891</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.027720152878175</v>
+        <v>-8.69212946841062</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.10291963675421</v>
+        <v>-6.71600374323976</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.601032372748094</v>
+        <v>-3.252659450922103</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.93238635808558</v>
+        <v>-7.881292732734401</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.009434</t>
+          <t>X ≈ 0.01107</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-9.74547084053517</v>
+        <v>0.6233073221214696</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-10.20257290878398</v>
+        <v>3.954843733888275</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-15.47549039586835</v>
+        <v>2.346597843040755</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-8.028164092529195</v>
+        <v>2.523681066938991</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.127560917357428</v>
+        <v>-1.789902403396859</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.486954191089907</v>
+        <v>-7.141151182230708</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.91485269691406</v>
+        <v>-2.783540070276445</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9350370750361492</v>
+        <v>-0.718963144442931</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.564987201390075</v>
+        <v>3.017523053464672</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-9.732185557149691</v>
+        <v>-1.629864097295567</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-5.058890100979454</v>
+        <v>-3.100388040365893</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-9.902555724121825</v>
+        <v>-0.5343643183902671</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.444761554578939</v>
+        <v>-0.9545151717037541</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.195040222302637</v>
+        <v>-0.7287795214772217</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.0105</t>
+          <t>X ≈ 0.01228</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-14.99343832021</v>
+        <v>-10.07759696467864</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-12.43834526650756</v>
+        <v>3.374388076897432</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-8.666547306437494</v>
+        <v>-1.297716791374903</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-8.536294173829958</v>
+        <v>-1.118518475734483</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.074715388902163</v>
+        <v>-2.721024874382259</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-8.777273451186502</v>
+        <v>-4.59756388822543</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-8.862007168458746</v>
+        <v>-2.508361204013376</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-5.162523900573575</v>
+        <v>-2.975429847800115</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-17.72352378675588</v>
+        <v>-0.8624989608446327</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-10.24031563845051</v>
+        <v>0.4614952863037729</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-14.61173562943481</v>
+        <v>4.604620215000111</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.41068580542269</v>
+        <v>8.986824454311879</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.497607083034247</v>
+        <v>6.392760557520333</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-14.74788575075793</v>
+        <v>4.444583164268607</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01157</t>
+          <t>X ≈ 0.01349</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-23.08167361432762</v>
+        <v>-0.1366723808439687</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.163835462585951</v>
+        <v>10.39671374901653</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-7.441057110359012</v>
+        <v>5.18708074414269</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>-3.137136169642936</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.96687225164721</v>
+        <v>6.080671838237038</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-7.55178325510802</v>
+        <v>8.817070258116033</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.754164031203921</v>
+        <v>11.17138428909374</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.221347429985421</v>
+        <v>5.826266864819189</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-8.164700257344151</v>
+        <v>5.765284708296413</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-9.014825442372079</v>
+        <v>4.915365911966553</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.337225825513137</v>
+        <v>4.710664753706361</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-9.185195609344227</v>
+        <v>4.745042906061684</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.723097279112608</v>
+        <v>1.885867662504367</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-9.355728888012877</v>
+        <v>2.1116033127309</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.01264</t>
+          <t>X ≈ 0.01469</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>9.045023218251622</v>
+        <v>-2.480916030534402</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.433449605287279</v>
+        <v>-4.092102123598231</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.038580898690689</v>
+        <v>13.37026934878958</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>9.929065920949476</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.75420256838936</v>
+        <v>12.96220493928228</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.927854753941709</v>
+        <v>13.25957896891737</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>14.53542872897712</v>
+        <v>13.17486860965123</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.37593763788793</v>
+        <v>16.27922853729306</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>14.00724544401336</v>
+        <v>5.503960666484559</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.15712025898543</v>
+        <v>11.79689901301185</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>20.64467462697556</v>
+        <v>18.7350549976088</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>28.37136547662863</v>
+        <v>15.19800457853555</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>27.95111086568372</v>
+        <v>14.77785372522209</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>20.50852450565233</v>
+        <v>22.14644651830577</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.0137</t>
+          <t>X ≈ 0.0159</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-7.038892865664486</v>
+        <v>5.413820811570943</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>14.32895050798076</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-9.045335185225404</v>
+        <v>-1.855294560984802</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.915082052617869</v>
+        <v>3.538088477340409</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3625941767809167</v>
+        <v>-7.526516865229013</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.06515223906531986</v>
+        <v>-7.229142835593926</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.941023134571559</v>
+        <v>-2.050695300123174</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.473839735790023</v>
+        <v>2.745393950826895</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.412839849607693</v>
+        <v>2.684411794304118</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.562714664579765</v>
+        <v>-3.428664896762591</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.35796134026215</v>
+        <v>6.892949734450866</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.392344497607645</v>
+        <v>6.927327886806225</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.972089886662744</v>
+        <v>6.507177033492894</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.221811218939067</v>
+        <v>11.9960705784563</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.01477</t>
+          <t>X ≈ 0.01711</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.062117235345539</v>
+        <v>4.661941112322822</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-20.77167859984098</v>
+        <v>-20.75876879026488</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>-21.15354017501989</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>-30.54712455524105</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>-21.56160458452722</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.0560598821469</v>
+        <v>-26.0261353167969</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23.08243727598562</v>
+        <v>-11.82513139034882</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>22.61525387720412</v>
+        <v>-2.768390510325986</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.55425399102182</v>
+        <v>-7.591277428753536</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>32.81523991710505</v>
+        <v>-8.441196225083395</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>32.61048659278744</v>
+        <v>-8.645897383343588</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>32.6448697501329</v>
+        <v>-8.611519230988264</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>32.224615139188</v>
+        <v>-9.031670084301673</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>43.58544758257536</v>
+        <v>-13.56783919597994</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-5 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-5 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,1561 +2210,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01568</t>
+          <t>X &gt; -0.01736</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1640</v>
+        <v>4089</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.645414004100552</v>
+        <v>0.2007026920400037</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.7327491594516</v>
+        <v>0.260494803980464</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.066790615439928</v>
+        <v>0.04971185750044071</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.7199924706669734</v>
+        <v>0.1688456581675624</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.5284866784398758</v>
+        <v>0.03429585471143071</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1702174901159381</v>
+        <v>0.05217982668788324</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3435450057482896</v>
+        <v>0.1028820025083661</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.107712694727077</v>
+        <v>-0.008927750863229278</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.232055170058779</v>
+        <v>0.0412626415002677</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3149652423505742</v>
+        <v>0.03552942730803466</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.09314940152493989</v>
+        <v>-0.03327344813900623</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3678029209636975</v>
+        <v>0.03929381972701407</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.8616250924685218</v>
+        <v>0.1218984335700313</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.9025207533071011</v>
+        <v>0.06804802758157535</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01462</t>
+          <t>X &gt; -0.01615</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1633</v>
+        <v>4058</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.676588503360158</v>
+        <v>0.1842767967808001</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.692061413931711</v>
+        <v>0.2322222007261416</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.086930120528301</v>
+        <v>0.04741009941281504</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.7349298895701608</v>
+        <v>0.1910409174377037</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.540302845631949</v>
+        <v>0.0103977103666395</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1817735529987488</v>
+        <v>0.02614491649661943</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3554872010586152</v>
+        <v>0.07787335398437989</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1166523409405826</v>
+        <v>-0.03123265505789874</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.245555610501327</v>
+        <v>0.01980047521140449</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.3208949938156707</v>
+        <v>0.09435979939434702</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.03605223490190923</v>
+        <v>0.02660880209045047</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.4267274952709386</v>
+        <v>0.05022132730402262</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.8632660299808705</v>
+        <v>0.1613049623319185</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.964504532973443</v>
+        <v>0.1546138069068235</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01355</t>
+          <t>X &gt; -0.01494</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1620</v>
+        <v>4031</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.462669089440737</v>
+        <v>0.09079514651807585</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.765110455341713</v>
+        <v>0.149797455921977</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.036826452578708</v>
+        <v>-0.008892310926206903</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.6750462263751444</v>
+        <v>0.1100677946016333</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.474551185289684</v>
+        <v>-0.09295771984074719</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.05395653821441471</v>
+        <v>-0.07911872853247104</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2283041493583511</v>
+        <v>-0.0265040642325971</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.0162677147161574</v>
+        <v>-0.1827835650460159</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.121117864485711</v>
+        <v>-0.08148461172582699</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.182223925516098</v>
+        <v>-0.02554743768739343</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1065452671311462</v>
+        <v>-0.06762224582204368</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5727606268208234</v>
+        <v>-0.06890059662650572</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.9544801059437802</v>
+        <v>0.07051245538087869</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.054583385044538</v>
+        <v>0.06224196076958322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01248</t>
+          <t>X &gt; -0.01373</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1602</v>
+        <v>3988</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.586779950577117</v>
+        <v>0.05594975301976035</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.863417910758294</v>
+        <v>0.08289787640181601</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.320553117977546</v>
+        <v>-0.1232826106287845</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.8204369716714126</v>
+        <v>-0.004472276720832724</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4248606774036148</v>
+        <v>-0.2039196541627746</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.127418739687954</v>
+        <v>-0.09305938372096278</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3028171373061284</v>
+        <v>-0.03897011732892963</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1126485888529132</v>
+        <v>-0.2169442933815233</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.199818234666083</v>
+        <v>-0.1139063150187809</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3032185288643134</v>
+        <v>-0.1484201968364189</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.05347543315622261</v>
+        <v>-0.1637172399256599</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4621567813937304</v>
+        <v>-0.1654039427677034</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8528815840483261</v>
+        <v>0.005085756164376676</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.013662314160911</v>
+        <v>0.01935094587423691</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01141</t>
+          <t>X &gt; -0.01252</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1582</v>
+        <v>3937</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.587956278622073</v>
+        <v>-0.02521982800271161</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.835150646919509</v>
+        <v>-0.0531049091135074</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.293071055912066</v>
+        <v>-0.2822129207139099</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.9017838753852701</v>
+        <v>-0.2395974400118845</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3052744473300706</v>
+        <v>-0.2826723324576079</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.007832509614409844</v>
+        <v>-0.2756373989985974</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3104824576280691</v>
+        <v>-0.1437346937390913</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1120188500685586</v>
+        <v>-0.2926348009917845</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.338495359718635</v>
+        <v>-0.1874939975728296</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.4829983084863017</v>
+        <v>-0.2622230372292051</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.007131500487339792</v>
+        <v>-0.1989551546754669</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4205418214461574</v>
+        <v>-0.3026663676799473</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.8215127316636099</v>
+        <v>-0.09916869369971693</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.9179381009066248</v>
+        <v>-0.03686927689719965</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01034</t>
+          <t>X &gt; -0.01131</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1557</v>
+        <v>3876</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.429417833654284</v>
+        <v>0.0518687470434287</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.702705719208822</v>
+        <v>0.04884437845943523</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.033512926766342</v>
+        <v>-0.2033643753457639</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6860913124163588</v>
+        <v>-0.05917023815652556</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1207789523320884</v>
+        <v>-0.120163143085783</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.09791339485236961</v>
+        <v>-0.1948862363202153</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2722635787151901</v>
+        <v>-0.1883262691243957</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1272448755575724</v>
+        <v>-0.3322383060130392</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.244062939515864</v>
+        <v>-0.1987300980459352</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2970122580482766</v>
+        <v>-0.2870479678423479</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2042677937573671</v>
+        <v>-0.1422329632058492</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6237600653518385</v>
+        <v>-0.2481016617945215</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.102093387654691</v>
+        <v>-0.08636382148186073</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.132011487520799</v>
+        <v>-0.07823282711656532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.009271</t>
+          <t>X &gt; -0.0101</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1526</v>
+        <v>3797</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.330146354174701</v>
+        <v>0.06501572799583499</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.752070756703638</v>
+        <v>0.1741094804973784</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.016220509051863</v>
+        <v>-0.02258779406751188</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5787778339607073</v>
+        <v>0.0694088981718437</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1246310163266031</v>
+        <v>0.1234540947511107</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2259945226697155</v>
+        <v>-0.1166177647037898</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.1344298731488323</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.07307819366723578</v>
+        <v>-0.2979098121303352</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.326994644647208</v>
+        <v>-0.1603513497474935</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2779711721767697</v>
+        <v>-0.2591388717553187</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2376422356602035</v>
+        <v>-0.1070502655490913</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6649527014535792</v>
+        <v>-0.1895034122891062</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.161528476887199</v>
+        <v>0.01068303388083081</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.187020321762823</v>
+        <v>-0.01202445501898808</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.008203</t>
+          <t>X &gt; -0.00889</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1495</v>
+        <v>3712</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.160104986876647</v>
+        <v>0.02915108355961138</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.670055295415729</v>
+        <v>0.2043533006767859</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.198346283533333</v>
+        <v>-0.1221139058820953</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.867292617236707</v>
+        <v>-0.004149708128643681</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.07149101709873662</v>
+        <v>0.09028110928268518</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04089364242509674</v>
+        <v>-0.108316576397506</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2894660024596689</v>
+        <v>-0.178375349938527</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1191037268929236</v>
+        <v>-0.4156150806274823</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.547053198520622</v>
+        <v>-0.3811617440615791</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5255206295378443</v>
+        <v>-0.3820952973064635</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.005020163791634502</v>
+        <v>-0.1949584613414004</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4404728398536406</v>
+        <v>-0.2801091225183754</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.9560471059140809</v>
+        <v>-0.03881358269213564</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.976751930401484</v>
+        <v>-0.06722343243309581</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.007134</t>
+          <t>X &gt; -0.007681</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1449</v>
+        <v>3593</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.149559365601995</v>
+        <v>0.153582028256551</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.937083509223783</v>
+        <v>0.2768299152367675</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.469598464960086</v>
+        <v>-0.04736185463513465</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.100529090095186</v>
+        <v>-0.06855510914454044</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2624878137702495</v>
+        <v>0.0467611382194022</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1037772485152715</v>
+        <v>-0.2237788285198263</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2187564797535444</v>
+        <v>-0.237829803047191</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3727237627376354</v>
+        <v>-0.4397013241763972</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.63731689020419</v>
+        <v>-0.4020982551385544</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.6943386269562595</v>
+        <v>-0.5417562155516364</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.002540227135895634</v>
+        <v>-0.2582709200775213</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3077049991750513</v>
+        <v>-0.3195793674211416</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8529676296094593</v>
+        <v>-0.1676904356809459</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.797317837923913</v>
+        <v>-0.2045534419343298</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.006065</t>
+          <t>X &gt; -0.006471</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1393</v>
+        <v>3440</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.064253770853753</v>
+        <v>0.3716759184954768</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.778598189437652</v>
+        <v>0.3401110861353089</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.38821278007147</v>
+        <v>0.04804390688873639</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.112648265932116</v>
+        <v>0.02016322943804028</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.07626633139798145</v>
+        <v>0.07751786642474912</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2211756063176793</v>
+        <v>-0.01519729889832178</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1108132811617324</v>
+        <v>-0.1711051149125851</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.6105525744087359</v>
+        <v>-0.5352976214002538</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.995403270256638</v>
+        <v>-0.4643163395282812</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.123864179818277</v>
+        <v>-0.572438966082224</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3243133434471872</v>
+        <v>-0.3834463093909122</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.07472215166847462</v>
+        <v>-0.6233617367296631</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5093273980752997</v>
+        <v>-0.3880033761188315</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2257921626184682</v>
+        <v>-0.5528890298669467</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.004996</t>
+          <t>X &gt; -0.005262</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1317</v>
+        <v>3230</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.644724250618452</v>
+        <v>0.3713812250931454</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.720454779502766</v>
+        <v>0.6888972594986669</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.493824621602769</v>
+        <v>0.2801736992987429</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.000967401183011</v>
+        <v>0.3347096599265029</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.02538407424155054</v>
+        <v>0.3381587169032585</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.04495718217206957</v>
+        <v>0.004042041360698079</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.001629195177592635</v>
+        <v>0.05977085599925402</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4999007011801311</v>
+        <v>-0.4521859073475909</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.188622421050304</v>
+        <v>-0.650819638218465</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.8384441159416482</v>
+        <v>-0.4325382164253853</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1327270305475423</v>
+        <v>-0.1560677985557533</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.205146263368448</v>
+        <v>-0.6303193252834021</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9229796645631509</v>
+        <v>-0.3833082325971944</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3052653502291562</v>
+        <v>-0.6974278735561938</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.003927</t>
+          <t>X &gt; -0.004052</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1224</v>
+        <v>2989</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.940956627777105</v>
+        <v>-0.1158260904943731</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.987748089526022</v>
+        <v>0.5896706188210175</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.626916470389716</v>
+        <v>0.3131264916467842</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.9494320674239063</v>
+        <v>0.4282799446716155</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.02205523689347189</v>
+        <v>0.2418199206984823</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1939534760664898</v>
+        <v>0.1238241664959219</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.153885252079121</v>
+        <v>0.02400078588620147</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3501258581592523</v>
+        <v>-0.1243011550513273</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.835768684715099</v>
+        <v>-0.3339055421231265</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.053240808518531</v>
+        <v>-0.2633845056746154</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2784022961014117</v>
+        <v>-0.04836746228425426</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1623864856947677</v>
+        <v>-0.3629640416106028</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5602160462174766</v>
+        <v>-0.09553375686098775</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1237027442219869</v>
+        <v>-0.5869091190310911</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.002858</t>
+          <t>X &gt; -0.002843</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1146</v>
+        <v>2781</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.32024423839971</v>
+        <v>-0.5812744534734264</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.711283710177717</v>
+        <v>-0.02254314188430584</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.193260430711597</v>
+        <v>-0.1468448139486256</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.407955033295728</v>
+        <v>0.1822823851454416</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.4655400114340935</v>
+        <v>-0.04928106215344741</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.777854171279408</v>
+        <v>-0.4144400103080486</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7284704058897589</v>
+        <v>-0.5156075808249696</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.195653804671259</v>
+        <v>-0.567955898824188</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.913148895735858</v>
+        <v>-0.7008029493462402</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.932410959578093</v>
+        <v>-0.7602079116840059</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.352508660530361</v>
+        <v>-0.477741551636349</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.7950217542747282</v>
+        <v>-0.8387623928108638</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2562528255509307</v>
+        <v>-0.7197328004017649</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.091690288279743</v>
+        <v>-1.157092804650986</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.00179</t>
+          <t>X &gt; -0.001633</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1058</v>
+        <v>2526</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.823315794291027</v>
+        <v>0.0447351139013179</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.595577970910078</v>
+        <v>0.5071872565834212</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.990446677506668</v>
+        <v>0.2129685137636841</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.162080337352002</v>
+        <v>0.522845906274263</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6627657033675618</v>
+        <v>0.04577354459004823</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.6483426335764335</v>
+        <v>-0.3468719151135673</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.5876917765796463</v>
+        <v>-0.3310084247068232</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.149303881687864</v>
+        <v>-0.3808426934152962</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.910020481751197</v>
+        <v>-0.4418248499380724</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.060428952898093</v>
+        <v>-0.223283021020606</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.415323920275171</v>
+        <v>-0.08917303089476292</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.908797231296127</v>
+        <v>-0.3715011334879748</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4791934853005131</v>
+        <v>-0.6332988593271125</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8379928711108064</v>
+        <v>-0.9222108733919541</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007207</t>
+          <t>X &gt; -0.0004236</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>945</v>
+        <v>2251</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.96862311429657</v>
+        <v>-0.0008451713669472838</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.202263518797913</v>
+        <v>0.2720981422414326</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.231381696853269</v>
+        <v>0.07872932852621517</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.07011879304808843</v>
+        <v>0.7209569567429028</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1511776862946874</v>
+        <v>-0.192187252376975</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.276568729551542</v>
+        <v>-0.2700006392241363</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1194743130227067</v>
+        <v>-0.3305868585040628</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6651694032191102</v>
+        <v>-0.2404135265515848</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.525111088343209</v>
+        <v>-0.3458203832076308</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.576294474429339</v>
+        <v>-0.1295463763389222</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>0.0211500664670865</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.3710032657401143</v>
+        <v>-0.2554446821105145</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1563372417643834</v>
+        <v>-0.5423214350240997</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5415365444087286</v>
+        <v>-0.7608327861303081</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0003481</t>
+          <t>X &gt; 0.000786</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>827</v>
+        <v>1950</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.829988380523609</v>
+        <v>0.4061560185203206</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.448007102256355</v>
+        <v>0.6113743590194076</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.050605277451986</v>
+        <v>0.3980369775802828</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7028362609526226</v>
+        <v>0.6075276843651309</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.04364209902054483</v>
+        <v>-0.4658544565190326</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5826299304560152</v>
+        <v>-0.1405966751107144</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6855542986915637</v>
+        <v>-0.4024177636371959</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5071430057731234</v>
+        <v>-0.02113776307324144</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.381927656163406</v>
+        <v>-0.2872481247242291</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.781025029824953</v>
+        <v>-0.4192182031053662</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7765885113372093</v>
+        <v>-0.008534745980938396</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6212863697112496</v>
+        <v>-0.4356950551640821</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.07418910641189314</v>
+        <v>-0.7532818059133888</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1872247269771989</v>
+        <v>-0.5788282069689075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001417</t>
+          <t>X &gt; 0.001995</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>732</v>
+        <v>1698</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9948007180301346</v>
+        <v>0.950169013453916</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.853988740814067</v>
+        <v>0.4853626651342182</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.067411335541621</v>
+        <v>0.2987988345710306</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6099086456334035</v>
+        <v>0.5787217879965922</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3377895135042479</v>
+        <v>-0.3387944728282193</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.04034757578858716</v>
+        <v>-0.1857991823431178</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.08608026323521045</v>
+        <v>-0.356200086220305</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6543271792621326</v>
+        <v>0.3276889108417649</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.31095548074498</v>
+        <v>-0.2633285813700539</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.204796512767452</v>
+        <v>-0.5243192269343098</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.36036950921617</v>
+        <v>0.03658621080079172</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.462598373728667</v>
+        <v>-0.4590709725329347</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.199792875383956</v>
+        <v>-0.7614361956932214</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.359907608681432</v>
+        <v>-0.7123789906963722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002486</t>
+          <t>X &gt; 0.003205</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>634</v>
+        <v>1420</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.921111276184817</v>
+        <v>0.4973600731797276</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.293988311126988</v>
+        <v>0.7466075538211712</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.791219222447992</v>
+        <v>0.5306703512959032</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9059630440177742</v>
+        <v>1.542228039729522</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8923006907394324</v>
+        <v>-0.5730826824424256</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.035062506818754</v>
+        <v>-0.2375076294350293</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5097068168198788</v>
+        <v>-0.3543361757111967</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2729339952108347</v>
+        <v>0.4140373904117709</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.015321894011436</v>
+        <v>-0.06947997737860589</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.603617426042511</v>
+        <v>-0.3560184920183289</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.231083684114033</v>
+        <v>0.4251958426792228</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.354429233393212</v>
+        <v>-0.03338375144432604</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.9860403112150848</v>
+        <v>-0.4535346047577349</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.524962512061826</v>
+        <v>-0.2982214897424669</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.003555</t>
+          <t>X &gt; 0.004415</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>534</v>
+        <v>1189</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.839232712733342</v>
+        <v>-0.2633428087770326</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.296023169129292</v>
+        <v>0.7655193169378265</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.627221463740852</v>
+        <v>1.338776114446446</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.622881856132558</v>
+        <v>2.186975796308964</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.148131053045411</v>
+        <v>-0.5708405207153007</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.007370743570057</v>
+        <v>0.2763856916064711</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.858966614312763</v>
+        <v>-0.4350076368944897</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.20451729792827</v>
+        <v>0.3594880591001015</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.414535022710972</v>
+        <v>-0.3743284119727193</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.766532866914929</v>
+        <v>-0.9719343403463157</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.09862701520253836</v>
+        <v>-0.5879054733752227</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.4387756930630999</v>
+        <v>-0.3012144530636363</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2645652016099689</v>
+        <v>-0.5531567277395268</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2347771365257216</v>
+        <v>-1.084359681381798</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.004623</t>
+          <t>X &gt; 0.005624</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>425</v>
+        <v>942</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.554471184059736</v>
+        <v>0.000604560806728216</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.163835462585993</v>
+        <v>1.451720474078691</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6175276985943512</v>
+        <v>2.067037696720774</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.042137198719026</v>
+        <v>1.3047272966108</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8566571601174502</v>
+        <v>-0.5517175788774935</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.330569686068408</v>
+        <v>0.6516407777342437</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.422306557031419</v>
+        <v>-0.7544610840096837</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.013946687661686</v>
+        <v>0.6892982976812831</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.811759080873564</v>
+        <v>-0.4332549841068811</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.485413677666187</v>
+        <v>-0.8585453303305854</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5136964137484767</v>
+        <v>-1.063246488590778</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2440191387559807</v>
+        <v>-0.3919256610762218</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.9827850738285164</v>
+        <v>-0.8120765143896307</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-1.117126426795792</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.005692</t>
+          <t>X &gt; 0.006834</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>329</v>
+        <v>730</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.584347411119069</v>
+        <v>0.4442540374928612</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9135225714721074</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.308391278068697</v>
+        <v>3.142554284562316</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.253472796788046</v>
+        <v>2.396421212315637</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.196802521627589</v>
+        <v>0.569542956456381</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.228298990556155</v>
+        <v>1.900384128190403</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.9277598021592581</v>
+        <v>0.5232052045631619</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.676381874502376</v>
+        <v>2.110931081324367</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.33598579283494</v>
+        <v>1.228031116582414</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.970305506738242</v>
+        <v>0.9260575257320056</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.871107463274669</v>
+        <v>-0.100561440747363</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.228821570366925</v>
+        <v>0.481761917087411</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4332707101872089</v>
+        <v>0.6095562692534529</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.095403481254387</v>
+        <v>0.1503604126306683</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.006761</t>
+          <t>X &gt; 0.008043</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>261</v>
+        <v>549</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.730079541584018</v>
+        <v>-0.3148510485848988</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>2.767103652575102</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2893913908805175</v>
+        <v>2.29431998170103</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.71849509820067</v>
+        <v>1.078134243930798</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.796932120676388</v>
+        <v>-0.8114533443578225</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.626941108200477</v>
+        <v>0.8569815663199876</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.00964034111977</v>
+        <v>-0.03746550432222762</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.458165754598795</v>
+        <v>1.863407564095034</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.200535281008783</v>
+        <v>1.073827957663326</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>0.9525066112423985</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.04343678435834875</v>
+        <v>0.565656090504973</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.460961704155892</v>
+        <v>0.2357355179058374</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.573274143019418</v>
+        <v>0.5441821145013535</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2904284254872778</v>
+        <v>0.2234696772961939</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.00783</t>
+          <t>X &gt; 0.009253</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>198</v>
+        <v>420</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.242182038802945</v>
+        <v>-2.127974854063766</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.437309641107703</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>-0.4774395460890659</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.206130068594256</v>
+        <v>-2.583598719374791</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.162658348471581</v>
+        <v>-4.657971093216005</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.985352811439761</v>
+        <v>-3.528680277774157</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.890518084066478</v>
+        <v>-2.063226628444013</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.443536705486999</v>
+        <v>-0.1493428912783656</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.342132778900648</v>
+        <v>-0.6865155239916305</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.9970580989232332</v>
+        <v>-2.012624796511965</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.812506794807675</v>
+        <v>-0.5506592881054857</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.341839447102601</v>
+        <v>-0.9924716119406369</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.436736351309207</v>
+        <v>0.01594896331737772</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.666255663383474</v>
+        <v>-1.186886815027513</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.008899</t>
+          <t>X &gt; 0.01046</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>149</v>
+        <v>317</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.16010498687664</v>
+        <v>-0.4559939121542982</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.427159584180941</v>
+        <v>2.60571719104356</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-4.164310169972161</v>
+        <v>-0.2812660317177134</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.691775158170032</v>
+        <v>-1.856648364764858</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.572478252436831</v>
+        <v>-2.54384073917717</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.261613495929225</v>
+        <v>-3.654167661810369</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3382165451877555</v>
+        <v>-0.423599168627284</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.555596904795522</v>
+        <v>0.6866192538320348</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.532248618970677</v>
+        <v>0.3101796840600457</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.053514743595919</v>
+        <v>-0.5397391122698139</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.7685775696703914</v>
+        <v>2.094676448712903</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5393211521788075</v>
+        <v>0.8672249480713745</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.396128934862872</v>
+        <v>1.077988921256392</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.380995370444737</v>
+        <v>0.988267158233711</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.009968</t>
+          <t>X &gt; 0.01167</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>108</v>
+        <v>238</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.419364246135899</v>
+        <v>-0.8142493638676811</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.5246176964553939</v>
+        <v>2.157897876401819</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.129748989858804</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6659238034596129</v>
+        <v>-3.310623260162345</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.982122796309561</v>
+        <v>-2.794097581726092</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.6846808585939</v>
+        <v>-2.496723552091005</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.712066905615295</v>
+        <v>0.3597425592310586</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.170809432759725</v>
+        <v>1.153178117124988</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.519820083052203</v>
+        <v>-0.5884763083053528</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.1778909029545375</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.980856963157834</v>
+        <v>3.819088611054177</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.015240120503265</v>
+        <v>1.33245836004815</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.372763287336149</v>
+        <v>1.752643641188534</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.06692906405687182</v>
+        <v>1.558211224188177</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01104</t>
+          <t>X &gt; 0.01288</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>1.405094332159948</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>1.866447099199746</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>-1.118997860684829</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>-3.835815031431522</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.527096341283105</v>
+        <v>-2.811604584527217</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-1.993397221558801</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.018945212493598</v>
+        <v>1.04689241917503</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>2.142323775388292</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>-0.5228250478011489</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.259684361549496</v>
+        <v>-0.3310771774643442</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.007311989612873</v>
+        <v>3.630888330942135</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.851218956482107</v>
+        <v>-0.5014001833692134</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.621440536013402</v>
+        <v>0.6409489633173777</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.299733296861106</v>
+        <v>0.8666846135439101</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01211</t>
+          <t>X &gt; 0.01409</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.715516903670625</v>
+        <v>1.82371973105505</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.596480604139195</v>
+        <v>-0.4497180176379203</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.201611897542605</v>
+        <v>-2.831244369280377</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.8542530898516034</v>
+        <v>-4.025522536950284</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.669242752086241</v>
+        <v>-5.226063745675127</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8792635009377392</v>
+        <v>-4.92868971604004</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.991226662387</v>
+        <v>-1.702141797160508</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.524043263605499</v>
+        <v>1.142047837198447</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.970506063990356</v>
+        <v>-2.230192597470023</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.120380878962429</v>
+        <v>-1.755608082541606</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.88577680837619</v>
+        <v>3.33770400423132</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.92015996572162</v>
+        <v>-1.925931088446475</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.49990535477672</v>
+        <v>0.302924680756675</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.764552060187341</v>
+        <v>0.5286603309832074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.01317</t>
+          <t>X &gt; 0.0153</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.91396908719743</v>
+        <v>2.803636814994107</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.15424732608502</v>
+        <v>0.3794425918489708</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.75937861948843</v>
+        <v>-6.519393833556471</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.185928048392235</v>
+        <v>-7.202176820049409</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.204345018531782</v>
+        <v>-9.366482633307712</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2.758754932667983</v>
+        <v>-9.069108603672625</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.415770609319004</v>
+        <v>-5.088778312532284</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.800439062389351</v>
+        <v>-2.303814435993822</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.03573547250334</v>
+        <v>-3.990812852679198</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.185610287475413</v>
+        <v>-4.840731649009058</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.536412518713391</v>
+        <v>-0.1673840267814413</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.718943824206974</v>
+        <v>-5.824062784995228</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.298689213262072</v>
+        <v>-2.992181117983428</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.696558693686512</v>
+        <v>-4.392461727919496</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.01424</t>
+          <t>X &gt; 0.01651</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.971677958859786</v>
+        <v>2.326776277157961</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.360104345895529</v>
+        <v>-2.169025200521254</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.29081703464778</v>
+        <v>-7.371488892968607</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.769907376557612</v>
+        <v>-9.164340672457165</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.41967662921224</v>
+        <v>-9.702630225552859</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.447816086845407</v>
+        <v>-9.405256195917772</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.769775777277651</v>
+        <v>-5.643812709030101</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.628173773844992</v>
+        <v>-3.226265968201446</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.916011096965022</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.065885911937094</v>
+        <v>-5.098705382592549</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.837876773666025</v>
+        <v>-1.457252694698887</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.546678535662615</v>
+        <v>-8.153643773112798</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.126423924717713</v>
+        <v>-4.72764078027236</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.050563861645159</v>
+        <v>-7.386520514661221</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01531</t>
+          <t>X &gt; 0.01772</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>9.271267562142967</v>
+        <v>1.735951439345165</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>13.54204689035519</v>
+        <v>2.534403900498212</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.26482524258212</v>
+        <v>-3.884463869799006</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.512725434013149</v>
+        <v>-3.754238726210644</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-6.702166833523201</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-7.55178325510807</v>
+        <v>-5.199973526779686</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.187012439384361</v>
+        <v>-4.07986460893742</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3.6610055111911</v>
+        <v>-3.342113975615725</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2.282347316167673</v>
+        <v>-4.607915409246935</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-4.25301492846836</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.545127115663291</v>
+        <v>0.3615610217051923</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3616661975795168</v>
+        <v>-8.037795765698526</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.7819208085244185</v>
+        <v>-3.638669510578197</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-5.82257241456854</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-5 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-5 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,1561 +3904,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01568</t>
+          <t>X &lt; -0.01736</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.2124440327312</v>
+        <v>-10.81424936386768</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.777341008002239</v>
+        <v>-11.23495926645533</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.1471781837586</v>
+        <v>-3.29639731787703</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>-7.928076936193428</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.85665716011745</v>
+        <v>-1.323509346431983</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.27174615665664</v>
+        <v>-1.026135316796896</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-2.301321866539247</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.6610055111911</v>
+        <v>3.183990442054963</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.482358566185262</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.632233381157334</v>
+        <v>2.273089489202327</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.427480056839755</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.520686743596954</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.159255662063821</v>
+        <v>-1.88881294144452</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.532199476248131</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01462</t>
+          <t>X &lt; -0.01615</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.92119582613149</v>
+        <v>-7.263524726186525</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4464753478083736</v>
+        <v>-7.135580384467744</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>11.35377789681455</v>
+        <v>-2.312960464874962</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.166957858690331</v>
+        <v>-6.530561408243116</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.06756103386207</v>
+        <v>-0.1123292222083805</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.486954191089929</v>
+        <v>0.1850448074267064</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.036803916426251</v>
+        <v>-0.7692307692307665</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.374061465280043</v>
+        <v>3.111526673939018</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.191110359585551</v>
+        <v>2.180979300024937</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.340985174557623</v>
+        <v>-0.4080699310875318</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.697207459996143</v>
+        <v>1.99592456282619</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.292566227097666</v>
+        <v>1.160737497790208</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.872311616152764</v>
+        <v>-2.737674225088419</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.756015832058743</v>
+        <v>-2.511938574861887</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01355</t>
+          <t>X &lt; -0.01494</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.210265383493734</v>
+        <v>-3.185141382647025</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>-3.387876771485509</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.611230471340292</v>
+        <v>-0.2615213956771569</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.185928048392235</v>
+        <v>-2.948197660539506</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.499358685171913</v>
+        <v>2.851540955378887</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.758754932667983</v>
+        <v>3.148914985013974</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>2.359979273635126</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.458820196869901</v>
+        <v>6.822488094637116</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.183883620651493</v>
+        <v>4.648829881776315</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.333758435623565</v>
+        <v>3.094685733333776</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>4.298435279298936</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.540315435052278</v>
+        <v>4.332813431654259</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.108718194145332</v>
+        <v>0.3915358177774735</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.562700565572754</v>
+        <v>0.6172714680040059</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01248</t>
+          <t>X &lt; -0.01373</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>-1.670105219723538</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.839432511270211</v>
+        <v>-1.119129150625206</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.77789713800696</v>
+        <v>2.269883248403538</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>0.2379462298297312</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>4.564521541598907</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4439401178531668</v>
+        <v>2.699733409071833</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.917562724014331</v>
+        <v>2.074482509265124</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.781920543870832</v>
+        <v>5.931738189802708</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>4.249134411658311</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.648573250438382</v>
+        <v>5.020837236950072</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6660421483430241</v>
+        <v>5.356676619230427</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.7004253056884551</v>
+        <v>5.39105477158575</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.727660675029092</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.247885750757938</v>
+        <v>1.412855784715084</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01141</t>
+          <t>X &lt; -0.01252</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>236</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.854387766746541</v>
+        <v>0.06145685082158536</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.329770675521424</v>
+        <v>1.416372452673002</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.456641099359608</v>
+        <v>4.411431576392538</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.326024666749724</v>
+        <v>4.117927906421585</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.647179157018094</v>
+        <v>4.850824794003849</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.436693741041573</v>
+        <v>5.148198823638936</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.434470936574712</v>
+        <v>3.368573210135487</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.359215229861171</v>
+        <v>5.867606261264001</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.55908490889626</v>
+        <v>4.535437664063252</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.882872767346591</v>
+        <v>5.804162935530009</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.330293356072495</v>
+        <v>4.752004150151173</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.364676513417926</v>
+        <v>6.481297556743783</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.031378424212157</v>
+        <v>3.095045008515115</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1071867130101793</v>
+        <v>2.049594218063689</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01034</t>
+          <t>X &lt; -0.01131</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>117</v>
+        <v>297</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.211387038158698</v>
+        <v>-0.9657645153828369</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.113558941721237</v>
+        <v>-0.2200482515443127</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.910375770485587</v>
+        <v>2.41548339400368</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3312271936913831</v>
+        <v>0.8622068540903669</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.044800858987628</v>
+        <v>1.670718647796008</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.328555502468554</v>
+        <v>2.978193687532112</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.703887510339115</v>
+        <v>3.230183664966283</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.247732509682798</v>
+        <v>5.120017378081897</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.041433478201348</v>
+        <v>3.712233874757771</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.046009147874287</v>
+        <v>4.882517098629933</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.577547595246713</v>
+        <v>2.994314256868051</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.543164437901282</v>
+        <v>4.375493756024731</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.963419048846184</v>
+        <v>2.271841219209634</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.568398571270755</v>
+        <v>2.160876532735834</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.009271</t>
+          <t>X &lt; -0.0101</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>148</v>
+        <v>376</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-0.88517134968329</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.7266335547958533</v>
+        <v>-1.432527655513077</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9055247656345813</v>
+        <v>0.03440308739146047</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9912491287849434</v>
+        <v>-0.6332441094457053</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.583724397911169</v>
+        <v>-1.1715336625414</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.934931108844154</v>
+        <v>1.519457388370284</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.668313474765078</v>
+        <v>1.966661922721137</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.108469846519554</v>
+        <v>3.627252853402474</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.208908645676523</v>
+        <v>2.502440909645664</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.358783460648596</v>
+        <v>3.514224240975373</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.548672566371692</v>
+        <v>1.979735848672632</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.514289409026262</v>
+        <v>2.81198634145349</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.934544019971163</v>
+        <v>0.7960908072890192</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.360498363370546</v>
+        <v>1.021826457515552</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.008203</t>
+          <t>X &lt; -0.00889</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>179</v>
+        <v>461</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.890086364902714</v>
+        <v>-0.4201785034193861</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.591045452727307</v>
+        <v>-1.380605377394282</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.924700365815774</v>
+        <v>0.8276601142064379</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.496294280546174</v>
+        <v>0.09020629900954447</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.952741459665667</v>
+        <v>-0.6650029937824584</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9793218683187135</v>
+        <v>1.150809213726809</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.064055585590992</v>
+        <v>1.933777813245896</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.7033978871358855</v>
+        <v>3.852826306118587</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.435694090339062</v>
+        <v>3.791844149595811</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.144228123188235</v>
+        <v>3.809604312051206</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7048379273622629</v>
+        <v>2.303384715613142</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.7392210847076939</v>
+        <v>2.988522087057397</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3189664737627922</v>
+        <v>1.049933055869801</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.01002858816199392</v>
+        <v>1.275668706096333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.007134</t>
+          <t>X &lt; -0.007681</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>225</v>
+        <v>580</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.60454943132109</v>
+        <v>-1.101605685706765</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1172102890479962</v>
+        <v>-1.505895227046459</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.833452693562514</v>
+        <v>0.1682989054398902</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.519261381725563</v>
+        <v>0.4709378421316899</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.130270944457713</v>
+        <v>-0.2397655040674422</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.721717895630945</v>
+        <v>1.609332663498677</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>1.869449890439405</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.170809432759725</v>
+        <v>3.12651917768715</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.998698435466309</v>
+        <v>3.065537021164374</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.48190658377171</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.610486592787467</v>
+        <v>2.183330859677767</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.533758639021784</v>
+        <v>2.562536598239987</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.113504028076882</v>
+        <v>1.625144365616237</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.363225360353169</v>
+        <v>1.850880015842769</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.006065</t>
+          <t>X &lt; -0.006471</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>281</v>
+        <v>733</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.738989921633461</v>
+        <v>-1.867000614436122</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.080100901145769</v>
+        <v>-1.431801987172527</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.372005481225614</v>
+        <v>-0.3258912436874652</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.858130499954115</v>
+        <v>-0.05924045207726891</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.883137690207029</v>
+        <v>-0.3246787091293086</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.941567638612362</v>
+        <v>0.2455466165494258</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.670429469763647</v>
+        <v>1.115815793436063</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.84459353714881</v>
+        <v>2.831557517998576</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.851209309329498</v>
+        <v>2.634149713453965</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.780443554906554</v>
+        <v>3.148487397342393</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.084587027741996</v>
+        <v>2.26165799897305</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.186585843450416</v>
+        <v>3.387441335503006</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.766331232505514</v>
+        <v>2.285162242080453</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.083668223144798</v>
+        <v>3.056600484394302</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.004996</t>
+          <t>X &lt; -0.005262</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>357</v>
+        <v>943</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.232934118529307</v>
+        <v>-1.367448374118659</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.443947507403919</v>
+        <v>-2.236322696238688</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9623042341787595</v>
+        <v>-1.040426000399876</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8124453219683332</v>
+        <v>-1.122289934224028</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.686760206829327</v>
+        <v>-1.130356793788444</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8290941794778135</v>
+        <v>0.1214180842029506</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>0.03670772493678243</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.700221197465602</v>
+        <v>1.79657439398143</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.319893580190872</v>
+        <v>2.583948547108712</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.469768395162944</v>
+        <v>1.840074289485102</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8930613602811164</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.459062093737003</v>
+        <v>2.51810759323029</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7586954379741755</v>
+        <v>1.673778585091853</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.96920108397596</v>
+        <v>2.747870544968443</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.003927</t>
+          <t>X &lt; -0.004052</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>450</v>
+        <v>1184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7156605424321967</v>
+        <v>0.2217866721683421</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7716785998408966</v>
+        <v>-1.389399420895487</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6112304713402921</v>
+        <v>-0.8551167515964622</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2970391595033419</v>
+        <v>-1.062729445845946</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.352493166679935</v>
+        <v>-0.5875054854281174</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.055051228964274</v>
+        <v>-0.2056719963335709</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.806451612903224</v>
+        <v>0.131914941697552</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8374760994263966</v>
+        <v>0.5094408925054097</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.220920657688531</v>
+        <v>1.124134411658311</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.370795472660603</v>
+        <v>0.9498912910041213</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.054931037231917</v>
+        <v>0.4073522949061044</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.200425305688455</v>
+        <v>1.201865582396557</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.780170694743553</v>
+        <v>0.5283363507047696</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>1.767585514444811</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.002858</t>
+          <t>X &lt; -0.002843</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>528</v>
+        <v>1392</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2292873768137511</v>
+        <v>1.100745860583132</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6119691989012352</v>
+        <v>0.1342589079204402</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.349175964002761</v>
+        <v>0.2409201879218514</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.102070606044222</v>
+        <v>-0.3451870467132778</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1910675901600243</v>
+        <v>0.1193887297039211</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.238449819253752</v>
+        <v>0.918195424095444</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3989991208493961</v>
+        <v>1.191651253941032</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.493430730806345</v>
+        <v>1.297648512733083</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>1.635553088399561</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.774835876701012</v>
+        <v>1.75898140694504</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.19129467359555</v>
+        <v>1.19560019129603</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.225677830940981</v>
+        <v>1.917315418449405</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.373605038177892</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.138477885605695</v>
+        <v>2.554903004348503</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.00179</t>
+          <t>X &lt; -0.001633</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>616</v>
+        <v>1647</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.52256453380221</v>
+        <v>-0.1201412121324168</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.05970448980853149</v>
+        <v>-0.7022716151235997</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3544882922680088</v>
+        <v>-0.3706507480626655</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3229291271408883</v>
+        <v>-0.7852197933362888</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1081325075379738</v>
+        <v>-0.05232290575401777</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7291990407228823</v>
+        <v>0.6082472497890592</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.002783867487899272</v>
+        <v>0.6446022658255544</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.887719211257831</v>
+        <v>0.7223278109008007</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.244008680776552</v>
+        <v>0.8768948189462833</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.179597781462917</v>
+        <v>0.5458167619295935</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.650169132470012</v>
+        <v>0.341115603669401</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.846889952153106</v>
+        <v>0.773678146931978</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.238323652896511</v>
+        <v>1.176952199563338</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.812720309848125</v>
+        <v>1.619948122954959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007207</t>
+          <t>X &lt; -0.0004236</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>729</v>
+        <v>1922</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.537154167204513</v>
+        <v>-0.04315669443476366</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9629354304419948</v>
+        <v>-0.253927849739263</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.1449281033985841</v>
+        <v>-0.1300270353241757</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.500775048146934</v>
+        <v>-0.82967741040801</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.6730760446398634</v>
+        <v>0.2399168539236811</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0342019586495752</v>
+        <v>0.381689223807733</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.006815911628173</v>
+        <v>0.5044477442096138</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7882284934072388</v>
+        <v>0.400449639841959</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9408597748879259</v>
+        <v>0.575871112032786</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.734570206298351</v>
+        <v>0.3260489907599506</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.118857977871187</v>
+        <v>0.1506394131932183</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.564200039326202</v>
+        <v>0.4742148547458243</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.239835839340209</v>
+        <v>0.8115807885903905</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.707532630586371</v>
+        <v>1.067213576429793</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0003481</t>
+          <t>X &lt; 0.000786</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>847</v>
+        <v>2223</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.846379496680562</v>
+        <v>-0.3947787492422989</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.869717815527174</v>
+        <v>-0.4806171527592369</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.4998806397708222</v>
+        <v>-0.3818936967785262</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.899039271869206</v>
+        <v>-0.5208475572278459</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7904016634119628</v>
+        <v>0.4213474118837226</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8459009021668962</v>
+        <v>0.1803634334434392</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.401222854733284</v>
+        <v>0.454558412894194</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4322935316996492</v>
+        <v>0.1220792711262959</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3189290434327674</v>
+        <v>0.4000878785902344</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.473520839536917</v>
+        <v>0.5181126893220664</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9149939303136776</v>
+        <v>0.1591340631972926</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.538999729168545</v>
+        <v>0.5334780937843462</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.826292288034956</v>
+        <v>0.81331107362913</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.908942269706451</v>
+        <v>0.6600381897922176</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001417</t>
+          <t>X &lt; 0.001995</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>942</v>
+        <v>2475</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.392909219680874</v>
+        <v>-0.6872844303731256</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.512419340581644</v>
+        <v>-0.2831541187614306</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.7432668831570624</v>
+        <v>-0.2345558944878476</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.565394702930512</v>
+        <v>-0.3864750475540575</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4106942248809915</v>
+        <v>0.2441189140620637</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2190723929854386</v>
+        <v>0.1787359908555501</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.7270865335381416</v>
+        <v>0.3358636001504465</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4518828790874068</v>
+        <v>-0.1312050436362924</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7679926501475833</v>
+        <v>0.3138685005859543</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.2508473166573</v>
+        <v>0.4948186810807655</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.197737682689677</v>
+        <v>0.1111647635490698</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.974432610978901</v>
+        <v>0.4509026695442628</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.508578848390307</v>
+        <v>0.6594600026280943</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.608802147331232</v>
+        <v>0.6255229973822978</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002486</t>
+          <t>X &lt; 0.003205</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1040</v>
+        <v>2753</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.212517898349958</v>
+        <v>-0.2880925437637885</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.276632259156976</v>
+        <v>-0.3407429354865457</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5209736407295935</v>
+        <v>-0.3005741245184979</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.541247833146066</v>
+        <v>-0.7865142582045053</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.06624622942629088</v>
+        <v>0.3062219226613792</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2481906771372806</v>
+        <v>0.1686557565733722</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.9081880569215457</v>
+        <v>0.2651704788584937</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1157870399254293</v>
+        <v>-0.1294081323077236</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2039497963372696</v>
+        <v>0.1558823488630949</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.37111567759176</v>
+        <v>0.3053709545632231</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.8781779152338345</v>
+        <v>-0.09658506044635828</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.584991428006738</v>
+        <v>0.1396690846283732</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.029290131182883</v>
+        <v>0.3572706771881116</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.335447582575398</v>
+        <v>0.2767978233756168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.003555</t>
+          <t>X &lt; 0.004415</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1140</v>
+        <v>2984</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.580850907622562</v>
+        <v>0.07675698852281698</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.832284660446959</v>
+        <v>-0.2639510035714352</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.353027492917676</v>
+        <v>-0.5584214856183465</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.659837297373116</v>
+        <v>-0.8628335870985211</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.624831939018712</v>
+        <v>0.2371249373718172</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.6770403509533907</v>
+        <v>-0.06730644924184759</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.414500606778986</v>
+        <v>0.2491868023244734</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6091088392776385</v>
+        <v>-0.06573085114459332</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3593695360985976</v>
+        <v>0.259731827407947</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6309960764194855</v>
+        <v>0.4993277756815786</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1633154953096181</v>
+        <v>0.3470402671099748</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.2329294661061141</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.179722744602351</v>
+        <v>0.334206919766288</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.392465126435049</v>
+        <v>0.5455273302552683</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.004623</t>
+          <t>X &lt; 0.005624</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1249</v>
+        <v>3231</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.613151009755072</v>
+        <v>-0.02645477706105481</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.830470831817493</v>
+        <v>-0.3861107709113369</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.145531078717354</v>
+        <v>-0.6264658493044308</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.855661026716398</v>
+        <v>-0.372707660626503</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7979130478540029</v>
+        <v>0.1699169308114676</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9793218683187135</v>
+        <v>-0.1503742650012541</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.660196731824058</v>
+        <v>0.2899308173632136</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.7260730612450814</v>
+        <v>-0.1292625699932373</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7435237867559152</v>
+        <v>0.2284883020134387</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.3263510282161519</v>
+        <v>0.3539756303666763</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2815977038985835</v>
+        <v>0.4140902480726254</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.7159808612440131</v>
+        <v>0.2185516157853442</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.8557262502991136</v>
+        <v>0.3418565540764575</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.311628527331202</v>
+        <v>0.4304806519221245</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.005692</t>
+          <t>X &lt; 0.006834</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1345</v>
+        <v>3443</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.530502812426427</v>
+        <v>-0.119281721638373</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.84407790797038</v>
+        <v>-0.6138412540329625</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.868301692402405</v>
+        <v>-0.6897720590778533</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.070887699898684</v>
+        <v>-0.5015759009967411</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4232451640442392</v>
+        <v>-0.1123292222083805</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7188351017918819</v>
+        <v>-0.3656798302544502</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6894057836912211</v>
+        <v>-0.04459308807133766</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4483442420732402</v>
+        <v>-0.3798444859434937</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6915772785835514</v>
+        <v>-0.1639213355041633</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3156526626886702</v>
+        <v>-0.09853801297348497</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.5566645686831251</v>
+        <v>0.1192685785722389</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.8882245462365788</v>
+        <v>-0.004151755696256032</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.210911985811748</v>
+        <v>-0.03050864411583376</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.354964311199936</v>
+        <v>0.06644983767015589</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.006761</t>
+          <t>X &lt; 0.008043</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1413</v>
+        <v>3624</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.458152505107648</v>
+        <v>0.02459057739516624</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.234863732750803</v>
+        <v>-0.3878884083682195</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.135731027914787</v>
+        <v>-0.3695504568522523</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.229189963056058</v>
+        <v>-0.1567034460097005</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7796083552630151</v>
+        <v>0.1312256734366102</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.8350245685706383</v>
+        <v>-0.09467212287156457</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8111597108316531</v>
+        <v>0.0684831196248652</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6748913917396848</v>
+        <v>-0.218213414694354</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9802423157516671</v>
+        <v>-0.0711682552963282</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.06233355452782519</v>
+        <v>-0.05142355747170058</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.08651991040494522</v>
+        <v>0.007456431300553845</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.4745098570007329</v>
+        <v>0.05735372359898605</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.7614688245565304</v>
+        <v>0.01135126216795612</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.9810597552576326</v>
+        <v>0.05956540824589496</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.00783</t>
+          <t>X &lt; 0.009253</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1476</v>
+        <v>3753</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.358303185074838</v>
+        <v>0.2178343018240625</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.077984906147201</v>
+        <v>-0.1293361661513686</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.135015774905952</v>
+        <v>0.03440308739146047</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.12638426392008</v>
+        <v>0.2976069543840794</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7188595330462988</v>
+        <v>0.5305939970330726</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8268230007360557</v>
+        <v>0.4290318564553814</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9428050048347103</v>
+        <v>0.2911300078275119</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7646889885303167</v>
+        <v>0.07811121885730188</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.330497381881166</v>
+        <v>0.164874526440471</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.2848879697527025</v>
+        <v>0.3145232572796957</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.286526872946375</v>
+        <v>0.1514554235938874</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2217899336881501</v>
+        <v>0.2008579169414872</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.5462882001975515</v>
+        <v>0.08876018690111209</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.7670193982935558</v>
+        <v>0.2230328682734637</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.008899</t>
+          <t>X &lt; 0.01046</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1525</v>
+        <v>3856</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.068323866318543</v>
+        <v>0.01584981681364184</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.587026321663444</v>
+        <v>-0.1842346287741705</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.5240794625308</v>
+        <v>0.004454475079349152</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4127929747892267</v>
+        <v>0.1605662352869217</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.02981916527268424</v>
+        <v>0.2176688644329943</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.06565220828592544</v>
+        <v>0.333836577733635</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.441413800221433</v>
+        <v>0.09380651875221702</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2836764873450619</v>
+        <v>0.003427693910651897</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9640218208319311</v>
+        <v>0.0603302228541196</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1517769784127552</v>
+        <v>0.1314660004285813</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.0125544535709281</v>
+        <v>-0.08458739679389282</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.5711840067223903</v>
+        <v>0.0161931292279931</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.7407065910592721</v>
+        <v>-0.0004713979305677185</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.093644303886876</v>
+        <v>0.006553216586787869</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.009968</t>
+          <t>X &lt; 0.01167</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1566</v>
+        <v>3935</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.270650287110037</v>
+        <v>0.0279537109760355</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.812018302600983</v>
+        <v>-0.09970668633582846</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.888415671617956</v>
+        <v>0.05166604539932251</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6116657237238314</v>
+        <v>0.2072461585617162</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.130978658541224</v>
+        <v>0.1760559969467437</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1027690116585092</v>
+        <v>0.1830600022132884</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5844418402242368</v>
+        <v>0.03614279969254142</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2518096148593187</v>
+        <v>-0.01105311710938395</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9797458671643398</v>
+        <v>0.1196241907775288</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1068334006287657</v>
+        <v>0.09614102512514933</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1201380969948431</v>
+        <v>-0.1450872065557505</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2971423162535842</v>
+        <v>0.005145621389068822</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.5788660077975152</v>
+        <v>-0.01962014237368237</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.9289980295741245</v>
+        <v>-0.008209499120219732</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01104</t>
+          <t>X &lt; 0.01288</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1590</v>
+        <v>3981</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.462090357827535</v>
+        <v>-0.08923058099766479</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.972013187879377</v>
+        <v>-0.05903599133365134</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.990470351188641</v>
+        <v>0.03580251269413282</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7309825887191579</v>
+        <v>0.1910840331304087</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2656396883584549</v>
+        <v>0.1426560671018535</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.03093300785734243</v>
+        <v>0.1279312233313092</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.709150922382193</v>
+        <v>0.006792954113180372</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3258404834881787</v>
+        <v>-0.04525460434584261</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.232323283927506</v>
+        <v>0.1082901052344738</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2596954834117469</v>
+        <v>0.1003584143382525</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3387417052780393</v>
+        <v>-0.09024620721047683</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1356163106469026</v>
+        <v>0.1088757811466436</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.5324578656353793</v>
+        <v>0.05445557640963017</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.6923658215691049</v>
+        <v>0.04324201118269855</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01211</t>
+          <t>X &lt; 0.01409</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1607</v>
+        <v>4022</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.679542538572257</v>
+        <v>-0.0893423006706584</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.963484931312031</v>
+        <v>0.04770947779001489</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.047987405754689</v>
+        <v>0.08788473612979431</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6762693445314127</v>
+        <v>0.1572405241240276</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2835918631417655</v>
+        <v>0.2030526551982419</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1102964182876818</v>
+        <v>0.21633189341226</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.7201852222890039</v>
+        <v>0.1204063184056068</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3458675923076129</v>
+        <v>0.01451013752004116</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.305613338994718</v>
+        <v>0.1658855307933393</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3522559369579668</v>
+        <v>0.1493935130473361</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3704420970964364</v>
+        <v>-0.04134251791915489</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.0370753886071995</v>
+        <v>0.1561130704412577</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4874675438314569</v>
+        <v>0.07312022854232936</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5860698601111807</v>
+        <v>0.06432674846850261</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.01317</t>
+          <t>X &lt; 0.0153</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1620</v>
+        <v>4050</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.585746012517667</v>
+        <v>-0.1058237342015929</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.888263164701321</v>
+        <v>0.01917311027675339</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.9752500978989</v>
+        <v>0.1794648319570555</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.6750462263751444</v>
+        <v>0.224632423412487</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3513984759300754</v>
+        <v>0.2910684876580518</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.05395653821441471</v>
+        <v>0.3063296553920765</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5979899164563065</v>
+        <v>0.2105036672236764</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2919936909558558</v>
+        <v>0.126791231009598</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.18280817910631</v>
+        <v>0.2027452357993482</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2439142401367107</v>
+        <v>0.2298400236538924</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2019063059718675</v>
+        <v>0.08837352709313251</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2643090537177883</v>
+        <v>0.2600550650677818</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.7077188474613578</v>
+        <v>0.1747574879615073</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.7459414097358916</v>
+        <v>0.2169932555192275</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.01424</t>
+          <t>X &lt; 0.01651</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1631</v>
+        <v>4069</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.61568770896303</v>
+        <v>-0.0801321010880045</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.872596031033559</v>
+        <v>0.08579545052580784</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.022816419587336</v>
+        <v>0.1699892367448115</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.730483776276472</v>
+        <v>0.2400665163334494</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3514737986880974</v>
+        <v>0.2546452111242417</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.05403186097243662</v>
+        <v>0.2712121726035761</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.533773794325775</v>
+        <v>0.1999632402414449</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.232946435784875</v>
+        <v>0.1390006670038346</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.11813162989317</v>
+        <v>0.214319036636752</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1912960306073686</v>
+        <v>0.212773587737388</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1509513157092641</v>
+        <v>0.1201237598877753</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3123534102636185</v>
+        <v>0.2911722803989036</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.7499419365736131</v>
+        <v>0.2043191516875709</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.7896168039119971</v>
+        <v>0.2719950911387272</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01531</t>
+          <t>X &lt; 0.01772</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1640</v>
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.584623730544322</v>
+        <v>-0.05467852748631685</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.976058161884701</v>
+        <v>0.005458852011578585</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.945136114223374</v>
+        <v>0.0874129029666193</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.6591652200587035</v>
+        <v>0.1089446074166958</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.285177676006775</v>
+        <v>0.1453354528985429</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.01226426170888573</v>
+        <v>0.1143501742745343</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4044092784202249</v>
+        <v>0.1162605510431689</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.107712694727077</v>
+        <v>0.1022447980230439</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.9883013614055187</v>
+        <v>0.1524895136452216</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.01027298153398704</v>
+        <v>0.1469897824574531</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.02872750280169356</v>
+        <v>0.05380346986497386</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.4896798252903238</v>
+        <v>0.2242008761254937</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.922563544631835</v>
+        <v>0.1357826634885697</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.024471972819299</v>
+        <v>0.1797146200670738</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_5.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_5.xlsx
@@ -575,46 +575,46 @@
         <v>31</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.350905368229192</v>
+        <v>2.32182144147697</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.961469771917962</v>
+        <v>3.960314001771614</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.3510194161962801</v>
+        <v>0.3508682922038844</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.736585377903232</v>
+        <v>-2.737099047323227</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.162640040231558</v>
+        <v>3.21109498661037</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.460233554306321</v>
+        <v>3.484160776730711</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.376594767358654</v>
+        <v>3.424536952430913</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.910856159521501</v>
+        <v>2.960041309452002</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.850729441507369</v>
+        <v>2.92390388290405</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-7.665556054184421</v>
+        <v>-7.566329029913369</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.872053171723074</v>
+        <v>-7.772235945285487</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.391152172127306</v>
+        <v>-1.267519610773071</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.036543299196673</v>
+        <v>-4.887894602177255</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-11.26369173054358</v>
+        <v>-11.09169297097545</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14.14074095267141</v>
+        <v>14.11176203794961</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.53793132315532</v>
+        <v>12.53684570046993</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.453151435583926</v>
+        <v>8.453060381996131</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.28002825640717</v>
+        <v>12.27961516339738</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>15.44098064244107</v>
+        <v>15.48950899626828</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>15.74161725398754</v>
+        <v>15.76561050731412</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.66103531074833</v>
+        <v>15.70903467538082</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>22.59475690650176</v>
+        <v>22.64402094723838</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.14128882498788</v>
+        <v>15.21450365400104</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17.99606619481996</v>
+        <v>18.09536042820974</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.09495525154384</v>
+        <v>14.19481540751205</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>17.83468337782008</v>
+        <v>17.95834093963666</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.71628998157871</v>
+        <v>13.86495070015305</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.9453883172493</v>
+        <v>14.1173870768126</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.322502803989117</v>
+        <v>3.293433150544722</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.354344505373128</v>
+        <v>6.35321138385688</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.60014292660565</v>
+        <v>10.60007031050836</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.73299347911266</v>
+        <v>10.73257260783916</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.19811656100224</v>
+        <v>10.2466137948123</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.213795989879607</v>
+        <v>1.237711368810601</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.129649883399097</v>
+        <v>1.177580299451321</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.985425379186637</v>
+        <v>3.034610300936507</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.925439870420902</v>
+        <v>2.998612788467476</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.37018659687807</v>
+        <v>11.46946249638106</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.844629765462329</v>
+        <v>8.94447873313247</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.88122369200412</v>
+        <v>9.004868651307298</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>6.138458419925925</v>
+        <v>6.287113570870055</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.040134225947007</v>
+        <v>4.212132985513669</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>51</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.321923095872158</v>
+        <v>6.292884638889397</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.58177957392778</v>
+        <v>10.58068475684816</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.14551407182524</v>
+        <v>12.14545731167935</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>18.14626826988506</v>
+        <v>18.14590324590665</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.875478276165545</v>
+        <v>5.923948425281267</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>14.00124740349555</v>
+        <v>14.02523420710885</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.048444340058914</v>
+        <v>8.096407173890853</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.626066068610236</v>
+        <v>5.675261013489809</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.566774199006318</v>
+        <v>5.639954700059768</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.636712795838065</v>
+        <v>8.735980025946731</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.556511590858243</v>
+        <v>2.656346258670489</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>10.43071697643807</v>
+        <v>10.55436319681251</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.053120444692112</v>
+        <v>8.201776232731014</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.359331672367439</v>
+        <v>4.531330431934101</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>61</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.923503711262072</v>
+        <v>-4.952642344447845</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.531062919485606</v>
+        <v>-6.532301957703247</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.292327049352707</v>
+        <v>-5.292517891566838</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-11.70411931528068</v>
+        <v>-11.70469424245763</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-10.60866607024776</v>
+        <v>-10.56030503396052</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.406645702956475</v>
+        <v>-5.38276884487523</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.689657866809291</v>
+        <v>2.737593130815164</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.223810862326523</v>
+        <v>2.272990139111066</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5264588783904003</v>
+        <v>0.5996193875277527</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.315177471894678</v>
+        <v>1.414421765225846</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.803138992974233</v>
+        <v>-3.703320187378623</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.769761449842534</v>
+        <v>-3.646136966467516</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.9128028693784387</v>
+        <v>-0.7641544312412236</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.591411389500195</v>
+        <v>2.763410149066857</v>
       </c>
     </row>
     <row r="11">
@@ -835,722 +835,722 @@
         <v>79</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.580018426074183</v>
+        <v>-0.6091138975983199</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.971808690377728</v>
+        <v>-5.973046683408938</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-8.892081832478979</v>
+        <v>-8.892305595475698</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.239106701938759</v>
+        <v>-6.239646253156621</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-11.82920937177793</v>
+        <v>-11.780866001656</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.956726574643987</v>
+        <v>-3.932844991400501</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.778764440253774</v>
+        <v>-2.730860504622378</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.982178701869309</v>
+        <v>-1.933020686012199</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.043339051073602</v>
+        <v>-1.970191753155781</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.628450978506621</v>
+        <v>-1.529219244274941</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.833229203746704</v>
+        <v>-1.733409480556944</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.064526388023623</v>
+        <v>-2.940903673333239</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.750755084927093</v>
+        <v>-4.602111099172248</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.260425091097446</v>
+        <v>-3.088426331530783</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.009495</t>
+          <t>X ≈ -0.009494</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>85</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.631245847375538</v>
+        <v>1.602177299735153</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.146655937219563</v>
+        <v>-1.14785271500012</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.323776053647052</v>
+        <v>4.323661295157784</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.281756505082178</v>
+        <v>3.281288434733284</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.572137883678138</v>
+        <v>1.620564509725973</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4791355410908835</v>
+        <v>-0.4552362265291663</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.784694948537762</v>
+        <v>1.832618903324331</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.842348501533365</v>
+        <v>4.891534779269584</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9.482568458416054</v>
+        <v>9.5557564182294</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.110440559372606</v>
+        <v>5.209688455504953</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.731952355404921</v>
+        <v>3.831781295536423</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.767301250900225</v>
+        <v>3.890931388071742</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.172229395279345</v>
+        <v>2.320876723172503</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.398547358641956</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.008286</t>
+          <t>X ≈ -0.008283</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>119</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.727826935735472</v>
+        <v>-3.756946327976316</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.983953221289468</v>
+        <v>-1.98515980703197</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.379123318741833</v>
+        <v>-2.379296114827014</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.940460425065815</v>
+        <v>1.939983979234214</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.404291664159842</v>
+        <v>1.452710881683714</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.377867220875714</v>
+        <v>3.401789272637188</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.616749440140723</v>
+        <v>1.664668068246797</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3116275502234274</v>
+        <v>0.3607887481837579</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2509801408088421</v>
+        <v>0.3241272839515759</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.43859108298679</v>
+        <v>4.537832078539452</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.716652162514542</v>
+        <v>1.816472034892691</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.9116269273608566</v>
+        <v>1.035248823663359</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.852400978558279</v>
+        <v>4.00104744506109</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.079219627549513</v>
+        <v>4.251218387115983</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.007076</t>
+          <t>X ≈ -0.007074</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>153</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.749966876461855</v>
+        <v>-4.779095948769864</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.14596242392011</v>
+        <v>-1.147163114975228</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.192432571250492</v>
+        <v>-2.192606731194658</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.063268081197435</v>
+        <v>-2.063778739733195</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6447626854825899</v>
+        <v>-0.5963696442915847</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.913455050075264</v>
+        <v>-4.889595146179396</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.73804501339395</v>
+        <v>-1.690154540511976</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.709653332360027</v>
+        <v>1.758815799552202</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.996792008264535</v>
+        <v>1.069934168338186</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1481043192536475</v>
+        <v>0.2473224111358974</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.556129989975261</v>
+        <v>2.655945652992457</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.510560177816217</v>
+        <v>6.634186724851318</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.785750839523736</v>
+        <v>4.93439504889929</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.627305528576748</v>
+        <v>7.799304288143411</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.005867</t>
+          <t>X ≈ -0.005864</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>210</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3762085836836775</v>
+        <v>0.3471496589362175</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-5.0245524375011</v>
+        <v>-5.02580529236775</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.522333376369794</v>
+        <v>-3.522527781962566</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.817860439503498</v>
+        <v>-4.818403963713067</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.931386643316117</v>
+        <v>-3.883042361219239</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3111166752632357</v>
+        <v>-0.2872332219895313</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.722197429413697</v>
+        <v>-3.674336227449771</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.813634937543675</v>
+        <v>-1.764502728435659</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.404282016515822</v>
+        <v>2.47741947954097</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.72424573461354</v>
+        <v>-2.625053851688051</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.880744356998356</v>
+        <v>-3.780958367508546</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.5163473984983753</v>
+        <v>-0.3927419396821605</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4602191550467865</v>
+        <v>-0.3115849836932227</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.670256042115234</v>
+        <v>1.842254801681896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.004657</t>
+          <t>X ≈ -0.004655</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>241</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>6.413964902649681</v>
+        <v>6.561948282239882</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.919554641181257</v>
+        <v>2.067132224976632</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1285229659639739</v>
+        <v>0.2453048941670133</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.8257948259787184</v>
+        <v>-0.6392482812222653</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.532999637467888</v>
+        <v>1.767311134651571</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.481554523075793</v>
+        <v>-1.270113035261261</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5034087795175708</v>
+        <v>0.5512793655836532</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.518773146407817</v>
+        <v>-4.469679426213268</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.581343427550166</v>
+        <v>-4.508264244585646</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.530465359305303</v>
+        <v>-2.431297336168505</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.491820101939638</v>
+        <v>-1.392045454249434</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.94619045764022</v>
+        <v>-3.822607067087048</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.952428182703173</v>
+        <v>-3.80380662839903</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.06813558009361</v>
+        <v>-1.896136820527047</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.003448</t>
+          <t>X ≈ -0.003445</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>6.107308031836148</v>
+        <v>5.9586581461596</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>8.775086332866714</v>
+        <v>8.616604224753942</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.463031303477784</v>
+        <v>6.342465789383382</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.717314622759631</v>
+        <v>3.651267943670696</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.133896042386951</v>
+        <v>4.104687395590567</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>7.320519722706649</v>
+        <v>7.201014453649734</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7.238668419654303</v>
+        <v>7.140275076353731</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.807448087411785</v>
+        <v>5.736307795769328</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.571583349643568</v>
+        <v>4.288554569795515</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.379239975633624</v>
+        <v>5.822769303245657</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.692446684293451</v>
+        <v>5.150081600153889</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.998551413619793</v>
+        <v>5.209852550923024</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8.25012749355686</v>
+        <v>7.174588457226939</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7.036556408415592</v>
+        <v>6.011167649840246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002238</t>
+          <t>X ≈ -0.002237</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.782451579703263</v>
+        <v>-6.413010337885638</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.269990147882339</v>
+        <v>-5.069796096454546</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.711113307287107</v>
+        <v>-3.516746944301019</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.191299788860078</v>
+        <v>-2.997627890671374</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.9908808136594658</v>
+        <v>-0.7615530306929017</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.083761612116795</v>
+        <v>-1.056281093399484</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.344225103783494</v>
+        <v>-2.285679973970545</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.421477298286341</v>
+        <v>-2.361523429204333</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.266209534071834</v>
+        <v>-3.179077656769003</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.078922710961429</v>
+        <v>-5.952705020820446</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.326855604158837</v>
+        <v>-4.207502684583417</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.467397455750529</v>
+        <v>-5.322078344868409</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.575937251988279</v>
+        <v>-1.423621876079849</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.483805582534515</v>
+        <v>-3.518608293556092</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001028</t>
+          <t>X ≈ -0.001027</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4178304671334701</v>
+        <v>0.7276602172462532</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.431498516161007</v>
+        <v>2.382493440315855</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.311777262743895</v>
+        <v>1.62882209713856</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.098783092289011</v>
+        <v>-0.7606486461166924</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.993590831763662</v>
+        <v>2.350096141958048</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9760982497576975</v>
+        <v>-0.9770498566511066</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3344591356974504</v>
+        <v>-0.3176748924046606</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.530319255634318</v>
+        <v>-1.667151100515682</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.227665048520812</v>
+        <v>-1.344506747509854</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.9905600653059352</v>
+        <v>-1.08575580851037</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9922177296639276</v>
+        <v>-1.289820897887424</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.321475940944879</v>
+        <v>-1.232472108088544</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.377990430622013</v>
+        <v>-1.267092766364797</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.243163871304567</v>
+        <v>-2.46236957514445</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0001812</t>
+          <t>X ≈ 0.0001826</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.637563843394034</v>
+        <v>-2.676909171254941</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.925870703994633</v>
+        <v>-1.934392988947806</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.989875042422057</v>
+        <v>-1.99585247484746</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.455797757861312</v>
+        <v>1.457026249153721</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.580739817646368</v>
+        <v>1.48143412148319</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.108331968198115</v>
+        <v>-0.9050998646275303</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1347628591358401</v>
+        <v>0.3634978282309262</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.660970798255121</v>
+        <v>-1.429829509252677</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.7252752139140242</v>
+        <v>-0.4701153162648382</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.747065125968582</v>
+        <v>2.034654598683218</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2134603132233437</v>
+        <v>0.5009149563941548</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9122902928211829</v>
+        <v>0.8919303004980534</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8243653531291173</v>
+        <v>0.8305926946222826</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.939932219235708</v>
+        <v>-1.919649960222834</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.00139</t>
+          <t>X ≈ 0.001392</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>252</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.259455352103693</v>
+        <v>-3.291039952161292</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.460453153531496</v>
+        <v>1.459143525041853</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.066713036428347</v>
+        <v>1.065763601494581</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8016245575150904</v>
+        <v>0.8005734951924097</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.321996727578622</v>
+        <v>-1.272552883500289</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1639821236219419</v>
+        <v>0.1868873369385113</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7138368757557316</v>
+        <v>-0.6653493063899703</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.371565113500594</v>
+        <v>-2.314435153103318</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.4484202858963826</v>
+        <v>-0.3750636046721496</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2889625050753395</v>
+        <v>0.3862905855426817</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3125640500101596</v>
+        <v>-0.2123459521999749</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2781858976549216</v>
+        <v>-0.1548482014420358</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5497800726636939</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.3210496929089928</v>
+        <v>0.4930484524756551</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0026</t>
+          <t>X ≈ 0.002602</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>278</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.263077988955132</v>
+        <v>3.235259309231246</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8490536727631763</v>
+        <v>-0.8504389822943352</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8855808551747444</v>
+        <v>-0.8854822864256917</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.342784965459387</v>
+        <v>-4.33690225154384</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8579294755609297</v>
+        <v>0.9031499274802073</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.078323101363722</v>
+        <v>0.101078097118787</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3657207801877362</v>
+        <v>-0.3182726762900216</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1133716682567893</v>
+        <v>-0.06279061752392323</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.253490515427082</v>
+        <v>-1.177281999228548</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.383984851325252</v>
+        <v>-1.282722838270566</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.948398239801278</v>
+        <v>-1.844628436585424</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.633444547877602</v>
+        <v>-2.506939166206912</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.334170940759364</v>
+        <v>-2.18451649711875</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.827859750964528</v>
+        <v>-2.655860991397816</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00381</t>
+          <t>X ≈ 0.003811</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.41283940931222</v>
+        <v>4.142694208494504</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6492651886882896</v>
+        <v>0.8423510701791699</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.628800438253876</v>
+        <v>-3.84375028984585</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.77640868136556</v>
+        <v>-1.56779657444595</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5846235062240268</v>
+        <v>-0.3399045537204159</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.882612212631301</v>
+        <v>-2.64254867395271</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.06089485176469367</v>
+        <v>0.3014520861673162</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.69481295287747</v>
+        <v>0.6939409918006803</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.499631662155608</v>
+        <v>1.322186856461599</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.814215030327873</v>
+        <v>2.649342551003343</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.460037899232795</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.3451907257217</v>
+        <v>1.21848000222856</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.05923900660742731</v>
+        <v>-0.03693368465165037</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.748178120037466</v>
+        <v>3.660809809892186</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.005019</t>
+          <t>X ≈ 0.00502</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>247</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.269976096825268</v>
+        <v>-1.511822539600956</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.851490764141921</v>
+        <v>-2.300548959169724</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.438642551555226</v>
+        <v>-1.48806025559584</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.551664406493884</v>
+        <v>5.095799996003244</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6437709304773023</v>
+        <v>-1.032070876537354</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.154749090305941</v>
+        <v>-1.166142839735556</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.7833127970428251</v>
+        <v>0.7943723630329345</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.8983307455293428</v>
+        <v>-0.8887538138788145</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1495963028618803</v>
+        <v>-0.1152904885043498</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.404373398786873</v>
+        <v>-1.525807717495368</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.224933540118919</v>
+        <v>1.500389867100573</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.04473679368886252</v>
+        <v>0.3468924732240382</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4343025395657421</v>
+        <v>0.5817013020460138</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9593950085883378</v>
+        <v>-0.7873962490216755</v>
       </c>
     </row>
     <row r="25">
@@ -1563,98 +1563,98 @@
         <v>212</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.527056373065328</v>
+        <v>-1.338990837897526</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.054389044702397</v>
+        <v>-3.869071846357642</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.636392063299624</v>
+        <v>-1.912403044484279</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.454407413127555</v>
+        <v>-2.251260494031882</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.412661875074328</v>
+        <v>-4.619243974744812</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.6482773629874</v>
+        <v>-3.407509994568898</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.153972360699179</v>
+        <v>-4.876693452960637</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.205946664863333</v>
+        <v>-3.935254969748378</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.153721274216245</v>
+        <v>-5.851799335693151</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-7.003640070546105</v>
+        <v>-6.676465333555242</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.378152549561015</v>
+        <v>-4.269899368285991</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.400378170790653</v>
+        <v>-3.27298953082569</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.707321476934247</v>
+        <v>-5.552372845658063</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.481585826707658</v>
+        <v>-5.309587067141017</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.007438</t>
+          <t>X ≈ 0.007439</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.746733000237015</v>
+        <v>2.68974006667613</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.911111927045901</v>
+        <v>3.833363610327758</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.715375457329429</v>
+        <v>5.631955021915758</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.394982237969081</v>
+        <v>6.313792465887737</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.758310741798944</v>
+        <v>4.732624295777285</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.065179744029379</v>
+        <v>5.001913379825645</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.223803100574628</v>
+        <v>2.20396735748114</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.861706832478532</v>
+        <v>3.375513650154225</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.695752300265184</v>
+        <v>2.244624049132817</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.8458335039352889</v>
+        <v>1.41879750559184</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.12129859355143</v>
+        <v>-1.524630837789253</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.227996685875723</v>
+        <v>1.582967703661552</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.8078458325623146</v>
+        <v>1.188793895880949</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.07139089290179612</v>
+        <v>0.3404232998504995</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.588342736695139</v>
+        <v>5.288898918650986</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>7.096665550375917</v>
+        <v>6.834431545227893</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.31865332799436</v>
+        <v>11.11673865849806</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>13.00005551980946</v>
+        <v>12.80204233592173</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>11.7120928147153</v>
+        <v>11.52997753706099</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>15.13588059360325</v>
+        <v>14.923388521256</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.558035830027791</v>
+        <v>6.28707558701408</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.416548581589822</v>
+        <v>8.165009447202991</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.805178828167818</v>
+        <v>6.567511362052997</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.42185531607477</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.20017127667856</v>
+        <v>3.981995264241249</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.234549429033883</v>
+        <v>4.039311028305448</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.264010978821261</v>
+        <v>2.087031518931191</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.815328024396671</v>
+        <v>4.684516706443951</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>103</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.273780277222045</v>
+        <v>-7.367907370289608</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.158663109665724</v>
+        <v>-2.20522494659339</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.081196867018399</v>
+        <v>-1.612098286135925</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.820911946669426</v>
+        <v>-5.342865301460435</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-11.16456645467533</v>
+        <v>-11.6413662984945</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.142471532730674</v>
+        <v>-3.6084437151411</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.109458713511053</v>
+        <v>-7.566301403452755</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.722158425258925</v>
+        <v>-3.200609320889214</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.754014368189523</v>
+        <v>-4.203886898615366</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.545680737334891</v>
+        <v>-6.964894234427526</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-8.69212946841062</v>
+        <v>-9.126773117143529</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.71600374323976</v>
+        <v>-7.122289989144662</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.252659450922103</v>
+        <v>-3.647659223532571</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-7.881292732734401</v>
+        <v>-7.709293973167739</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.6233073221214696</v>
+        <v>0.5763079281993839</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.954843733888275</v>
+        <v>3.93140244798186</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.346597843040755</v>
+        <v>2.303096558432543</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.523681066938991</v>
+        <v>2.43298059964728</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.789902403396859</v>
+        <v>-1.759972245008413</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-7.141151182230708</v>
+        <v>-7.660026232362291</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.783540070276445</v>
+        <v>-4.016978617884028</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.718963144442931</v>
+        <v>-2.013675575798231</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.017523053464672</v>
+        <v>1.653055518768632</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.629864097295567</v>
+        <v>-2.874476765750089</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.100388040365893</v>
+        <v>-4.313185114520678</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5343643183902671</v>
+        <v>-1.785882574686646</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9545151717037541</v>
+        <v>-2.181040501250543</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7287795214772217</v>
+        <v>-1.931995639235076</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-10.07759696467864</v>
+        <v>-9.956920335525254</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.374388076897432</v>
+        <v>3.353519600595469</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.297716791374903</v>
+        <v>-1.295537536655416</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.118518475734483</v>
+        <v>-1.165653495440765</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.721024874382259</v>
+        <v>-3.782562210860675</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.59756388822543</v>
+        <v>-5.637436266509837</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.508361204013376</v>
+        <v>-3.570432781267328</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.975429847800115</v>
+        <v>-4.036265541650614</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.8624989608446327</v>
+        <v>-1.945578576319328</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4614952863037729</v>
+        <v>-0.6417475826661629</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.604620215000111</v>
+        <v>3.409431118733856</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.986824454311879</v>
+        <v>7.722917005034859</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.392760557520333</v>
+        <v>5.200099504003063</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.444583164268607</v>
+        <v>3.321484791550233</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1366723808439687</v>
+        <v>-0.1291594439345971</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.39671374901653</v>
+        <v>10.19242537567148</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.18708074414269</v>
+        <v>5.036782625452012</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.137136169642936</v>
+        <v>-4.357142857142897</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.080671838237038</v>
+        <v>4.677417525714745</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.817070258116033</v>
+        <v>7.331155425486052</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.17138428909374</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.826266864819189</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.765284708296413</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.915365911966553</v>
+        <v>3.56291300497309</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.710664753706361</v>
+        <v>3.358772557437</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.745042906061684</v>
+        <v>3.416939294801892</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.885867662504367</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.1116033127309</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>28</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.480916030534402</v>
+        <v>-2.510111824887034</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598231</v>
+        <v>-4.093288910042887</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>13.37026934878958</v>
+        <v>13.37011595878526</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.929065920949476</v>
+        <v>9.928571428571473</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>12.96220493928228</v>
+        <v>13.01075085904805</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>13.25957896891737</v>
+        <v>13.28353637786698</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>13.17486860965123</v>
+        <v>13.22288028864155</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>16.27922853729306</v>
+        <v>16.32847609968677</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.503960666484559</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.79689901301185</v>
+        <v>11.89624633830643</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>18.7350549976088</v>
+        <v>18.83496303362747</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>15.19800457853555</v>
+        <v>15.3217011995638</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>14.77785372522209</v>
+        <v>14.92654327299991</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>22.14644651830577</v>
+        <v>22.31844527787243</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>19</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.413820811570943</v>
+        <v>5.384625017218312</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>14.32895050798076</v>
+        <v>14.32776372153611</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.855294560984802</v>
+        <v>-1.855447950989124</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.538088477340409</v>
+        <v>3.537593984962406</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-7.526516865229013</v>
+        <v>-7.477970945463241</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-7.229142835593926</v>
+        <v>-7.205185426644313</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.050695300123174</v>
+        <v>-2.002683621132853</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.745393950826895</v>
+        <v>2.794641513220611</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.684411794304118</v>
+        <v>2.757668904083815</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.428664896762591</v>
+        <v>-3.329317571468017</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.892949734450866</v>
+        <v>6.992857770469541</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.927327886806225</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.507177033492894</v>
+        <v>6.655866581270722</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.9960705784563</v>
+        <v>12.16806933802297</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>21</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.661941112322822</v>
+        <v>4.632745317970191</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-20.75876879026488</v>
+        <v>-20.75995557670954</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-21.15354017501989</v>
+        <v>-21.15369356502421</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-30.54712455524105</v>
+        <v>-30.54761904761905</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-21.56160458452722</v>
+        <v>-21.51305866476145</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-26.0261353167969</v>
+        <v>-26.00217790784728</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-11.82513139034882</v>
+        <v>-11.77711971135849</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.768390510325986</v>
+        <v>-2.719142947932269</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7.591277428753536</v>
+        <v>-7.518020318973839</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-8.441196225083395</v>
+        <v>-8.341848899788822</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-8.645897383343588</v>
+        <v>-8.545989347324912</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.611519230988264</v>
+        <v>-8.48782260996002</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-9.031670084301673</v>
+        <v>-8.882980536523846</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-13.56783919597994</v>
+        <v>-13.39584043641327</v>
       </c>
     </row>
   </sheetData>
@@ -2210,105 +2210,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01736</t>
+          <t>X &gt; -0.01735</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2007026920400037</v>
+        <v>0.2008047809967977</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.260494803980464</v>
+        <v>0.2598239304240835</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04971185750044071</v>
+        <v>0.049582199185636</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1688456581675624</v>
+        <v>0.1684045881126153</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.03429585471143071</v>
+        <v>0.03314073493029213</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.05217982668788324</v>
+        <v>0.05151523445345418</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1028820025083661</v>
+        <v>0.1015543294777501</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.008927750863229278</v>
+        <v>-0.009983297710768113</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.0412626415002677</v>
+        <v>0.03954594748402229</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.03552942730803466</v>
+        <v>0.03325552794719755</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.03327344813900623</v>
+        <v>-0.03537574287751966</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.03929381972701407</v>
+        <v>0.03647448088997862</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1218984335700313</v>
+        <v>0.1183083477204221</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.06804802758157535</v>
+        <v>0.06408987717561132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01615</t>
+          <t>X &gt; -0.01614</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4058</v>
+        <v>4069</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1842767967808001</v>
+        <v>0.1846456469405524</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2322222007261416</v>
+        <v>0.231631452613378</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.04741009941281504</v>
+        <v>0.04728682713265187</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1910409174377037</v>
+        <v>0.1905403985570686</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.0103977103666395</v>
+        <v>0.008929237805176626</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02614491649661943</v>
+        <v>0.02536335148206348</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.07787335398437989</v>
+        <v>0.07623792217582803</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.03123265505789874</v>
+        <v>-0.03261066630797416</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.01980047521140449</v>
+        <v>0.0175712372362824</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.09435979939434702</v>
+        <v>0.09115356709531142</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.02660880209045047</v>
+        <v>0.02356814168248889</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.05022132730402262</v>
+        <v>0.04640906354948271</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1613049623319185</v>
+        <v>0.1564485029051923</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1546138069068235</v>
+        <v>0.1490810957287394</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4031</v>
+        <v>4042</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09079514651807585</v>
+        <v>0.09161443898477728</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.149797455921977</v>
+        <v>0.1494343262669844</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.008892310926206903</v>
+        <v>-0.008862575633628467</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1100677946016333</v>
+        <v>0.1097870540121235</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09295771984074719</v>
+        <v>-0.09447889022018785</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.07911872853247104</v>
+        <v>-0.07977931878203037</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0265040642325971</v>
+        <v>-0.02818699428546267</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1827835650460159</v>
+        <v>-0.1840874237463126</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.08148461172582699</v>
+        <v>-0.08394216584452607</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.02554743768739343</v>
+        <v>-0.02911204033915027</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.06762224582204368</v>
+        <v>-0.07109382669391096</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.06890059662650572</v>
+        <v>-0.07324015976924869</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.07051245538087869</v>
+        <v>0.06487760747577909</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.06224196076958322</v>
+        <v>0.05577474701787821</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3988</v>
+        <v>3999</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.05594975301976035</v>
+        <v>0.05718628079596044</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.08289787640181601</v>
+        <v>0.0827270460778351</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1232826106287845</v>
+        <v>-0.1229371227964435</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.004472276720832724</v>
+        <v>-0.004436446566657537</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2039196541627746</v>
+        <v>-0.2056734352205325</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.09305938372096278</v>
+        <v>-0.09394588531528569</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.03897011732892963</v>
+        <v>-0.04115223400306434</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2169442933815233</v>
+        <v>-0.2186970766998897</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1139063150187809</v>
+        <v>-0.1170879180414346</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1484201968364189</v>
+        <v>-0.1527526267554933</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1637172399256599</v>
+        <v>-0.1680354671221522</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1654039427677034</v>
+        <v>-0.1708542330066365</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.005085756164376676</v>
+        <v>-0.002028155571466073</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.01935094587423691</v>
+        <v>0.01108272294803214</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3937</v>
+        <v>3948</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.02521982800271161</v>
+        <v>-0.02336605361710298</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0531049091135074</v>
+        <v>-0.05288486963879535</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2822129207139099</v>
+        <v>-0.2814194217220347</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2395974400118845</v>
+        <v>-0.2389013210135005</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2826723324576079</v>
+        <v>-0.2848554805309647</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2756373989985974</v>
+        <v>-0.2763365096095214</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1437346937390913</v>
+        <v>-0.1462726822813352</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2926348009917845</v>
+        <v>-0.2948348331840975</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1874939975728296</v>
+        <v>-0.1914570096126482</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2622230372292051</v>
+        <v>-0.2675766807797615</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1989551546754669</v>
+        <v>-0.204520641391511</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3026663676799473</v>
+        <v>-0.3094018745772544</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.09916869369971693</v>
+        <v>-0.1080043520769038</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.03686927689719965</v>
+        <v>-0.04730953469084653</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3876</v>
+        <v>3887</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.0518687470434287</v>
+        <v>0.05399073921558539</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.04884437845943523</v>
+        <v>0.0487988047558332</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2033643753457639</v>
+        <v>-0.2027785658793491</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.05917023815652556</v>
+        <v>-0.05896477143591028</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.120163143085783</v>
+        <v>-0.1235993902919077</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1948862363202153</v>
+        <v>-0.1961995473117994</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1883262691243957</v>
+        <v>-0.1915301596672094</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.3322383060130392</v>
+        <v>-0.335132575224236</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1987300980459352</v>
+        <v>-0.2038716379186809</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2870479678423479</v>
+        <v>-0.2939728488287301</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1422329632058492</v>
+        <v>-0.1496128018481073</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2481016617945215</v>
+        <v>-0.2570373670893957</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.08636382148186073</v>
+        <v>-0.09770716791713596</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.07823282711656532</v>
+        <v>-0.09141910523604935</v>
       </c>
     </row>
     <row r="12">
@@ -2526,725 +2526,725 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3797</v>
+        <v>3808</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.06501572799583499</v>
+        <v>0.06774737427554101</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1741094804973784</v>
+        <v>0.1737267967634537</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.02258779406751188</v>
+        <v>-0.02250739063300244</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.0694088981718437</v>
+        <v>0.06925840005986572</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1234540947511107</v>
+        <v>0.1182399117820907</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1166177647037898</v>
+        <v>-0.1186798545379091</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1344298731488323</v>
+        <v>-0.1388497244646203</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2979098121303352</v>
+        <v>-0.3019831107409772</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1603513497474935</v>
+        <v>-0.1672279170405986</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2591388717553187</v>
+        <v>-0.268346676234124</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1070502655490913</v>
+        <v>-0.1167556753727936</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1895034122891062</v>
+        <v>-0.2013584179840109</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.01068303388083081</v>
+        <v>-0.004259712410522809</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.01202445501898808</v>
+        <v>-0.02924379775777197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.00889</t>
+          <t>X &gt; -0.008888</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3712</v>
+        <v>3723</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.02915108355961138</v>
+        <v>0.03271472757554506</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2043533006767859</v>
+        <v>0.2038998449772365</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1221139058820953</v>
+        <v>-0.1217349861990016</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.004149708128643681</v>
+        <v>-0.004075618996601804</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.09028110928268518</v>
+        <v>0.08394026342719485</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.108316576397506</v>
+        <v>-0.1109959191043188</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.178375349938527</v>
+        <v>-0.1838604237292003</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4156150806274823</v>
+        <v>-0.4205565785494443</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3811617440615791</v>
+        <v>-0.3892138607682298</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3820952973064635</v>
+        <v>-0.3934159714793068</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1949584613414004</v>
+        <v>-0.2069049212839573</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2801091225183754</v>
+        <v>-0.2947896920948736</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.03881358269213564</v>
+        <v>-0.05734501915900125</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.06722343243309581</v>
+        <v>-0.08859973191225379</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.007681</t>
+          <t>X &gt; -0.007679</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3593</v>
+        <v>3604</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.153582028256551</v>
+        <v>0.1578450454475444</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2768299152367675</v>
+        <v>0.2761801165058415</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.04736185463513465</v>
+        <v>-0.04719287346127743</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.06855510914454044</v>
+        <v>-0.06826626610799735</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.0467611382194022</v>
+        <v>0.0387450071640103</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2237788285198263</v>
+        <v>-0.2269841093976694</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.237829803047191</v>
+        <v>-0.2448967418604866</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4397013241763972</v>
+        <v>-0.4463557166962886</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4020982551385544</v>
+        <v>-0.4127675778108681</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5417562155516364</v>
+        <v>-0.556240199545968</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.2582709200775213</v>
+        <v>-0.2737145377614922</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3195793674211416</v>
+        <v>-0.3387060581812378</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1676904356809459</v>
+        <v>-0.1913485439209737</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2045534419343298</v>
+        <v>-0.2318956132009262</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.006471</t>
+          <t>X &gt; -0.006469</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3440</v>
+        <v>3451</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3716759184954768</v>
+        <v>0.3767242028266438</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3401110861353089</v>
+        <v>0.3392840036158375</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.04804390688873639</v>
+        <v>0.04792399707861961</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.02016322943804028</v>
+        <v>0.02020473025962133</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.07751786642474912</v>
+        <v>0.06690279959308043</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.01519729889832178</v>
+        <v>-0.02026736392458872</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1711051149125851</v>
+        <v>-0.1808212729547591</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5352976214002538</v>
+        <v>-0.5441219415546001</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.4643163395282812</v>
+        <v>-0.4785031232066359</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.572438966082224</v>
+        <v>-0.5918661280983741</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3834463093909122</v>
+        <v>-0.4036009501594435</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6233617367296631</v>
+        <v>-0.6478490879708545</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3880033761188315</v>
+        <v>-0.4185982598588254</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5528890298669467</v>
+        <v>-0.58795866301422</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.005262</t>
+          <t>X &gt; -0.00526</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3230</v>
+        <v>3241</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3713812250931454</v>
+        <v>0.3786404799685741</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6888972594986669</v>
+        <v>0.6869139795974917</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2801736992987429</v>
+        <v>0.2792707646190848</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3347096599265029</v>
+        <v>0.3337214922880847</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3381587169032585</v>
+        <v>0.3228387711359915</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.004042041360698079</v>
+        <v>-0.002969360162275336</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.05977085599925402</v>
+        <v>0.04554038716371167</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4521859073475909</v>
+        <v>-0.4650475925126258</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.650819638218465</v>
+        <v>-0.6700315855876937</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4325382164253853</v>
+        <v>-0.4601261028117776</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1560677985557533</v>
+        <v>-0.184765696335532</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6303193252834021</v>
+        <v>-0.6643787088102897</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3833082325971944</v>
+        <v>-0.4255321654419078</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6974278735561938</v>
+        <v>-0.7454238983077062</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.004052</t>
+          <t>X &gt; -0.00405</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2989</v>
+        <v>3000</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1158260904943731</v>
+        <v>-0.1180852468138909</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5896706188210175</v>
+        <v>0.576036447218705</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3131264916467842</v>
+        <v>0.2819993562120757</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4282799446716155</v>
+        <v>0.4118833974267559</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2418199206984823</v>
+        <v>0.2067994912669135</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1238241664959219</v>
+        <v>0.09882451507066747</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.02400078588620147</v>
+        <v>0.004912689230643252</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1243011550513273</v>
+        <v>-0.1433421685386804</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3339055421231265</v>
+        <v>-0.361693561981518</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2633845056746154</v>
+        <v>-0.3017753470654583</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.04836746228425426</v>
+        <v>-0.08778088911645199</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3629640416106028</v>
+        <v>-0.4106676973620651</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.09553375686098775</v>
+        <v>-0.1541441169176778</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5869091190310911</v>
+        <v>-0.6529832935560833</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.002843</t>
+          <t>X &gt; -0.002841</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2781</v>
+        <v>2788</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5812744534734264</v>
+        <v>-0.5801618606267951</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.02254314188430584</v>
+        <v>-0.03536971090090191</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1468448139486256</v>
+        <v>-0.1788395547751236</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1822823851454416</v>
+        <v>0.1655600388170981</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.04928106215344741</v>
+        <v>-0.0895965760633004</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4144400103080486</v>
+        <v>-0.4412272306175424</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5156075808249696</v>
+        <v>-0.5376614951560512</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.567955898824188</v>
+        <v>-0.5904317641029806</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7008029493462402</v>
+        <v>-0.7152992305384558</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7602079116840059</v>
+        <v>-0.7674867767160904</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.477741551636349</v>
+        <v>-0.4860688545846372</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8387623928108638</v>
+        <v>-0.8380530247065536</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7197328004017649</v>
+        <v>-0.711422203617353</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.157092804650986</v>
+        <v>-1.159726478635001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001633</t>
+          <t>X &gt; -0.001632</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2526</v>
+        <v>2532</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.0447351139013179</v>
+        <v>0.009573214483097559</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5071872565834212</v>
+        <v>0.4736402238154298</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2129685137636841</v>
+        <v>0.1586423929810437</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.522845906274263</v>
+        <v>0.4853768278965092</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.04577354459004823</v>
+        <v>-0.02165785079269256</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3468719151135673</v>
+        <v>-0.3790416899887248</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3310084247068232</v>
+        <v>-0.360926609462318</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3808426934152962</v>
+        <v>-0.4113640444086926</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4418248499380724</v>
+        <v>-0.4661968304140416</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.223283021020606</v>
+        <v>-0.2432309036944815</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.08917303089476292</v>
+        <v>-0.1098101419149344</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3715011334879748</v>
+        <v>-0.3846918548955571</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6332988593271125</v>
+        <v>-0.6394146537949084</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9222108733919541</v>
+        <v>-0.9212297390537216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0004236</t>
+          <t>X &gt; -0.0004221</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2251</v>
+        <v>2255</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0008451713669472838</v>
+        <v>-0.07863525547937655</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2720981422414326</v>
+        <v>0.2391602499925298</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.07872932852621517</v>
+        <v>-0.02195174362721986</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7209569567429028</v>
+        <v>0.638436276367301</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.192187252376975</v>
+        <v>-0.3129996938046418</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2700006392241363</v>
+        <v>-0.3055834806027065</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3305868585040628</v>
+        <v>-0.3662395698281671</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.2404135265515848</v>
+        <v>-0.2571055013747099</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3458203832076308</v>
+        <v>-0.3583068760745505</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1295463763389222</v>
+        <v>-0.1397367136128835</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0211500664670865</v>
+        <v>0.03514018154599086</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2554446821105145</v>
+        <v>-0.2805521076075479</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5423214350240997</v>
+        <v>-0.5623118435147134</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7608327861303081</v>
+        <v>-0.7319189920039904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.000786</t>
+          <t>X &gt; 0.0007873</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4061560185203206</v>
+        <v>0.3200768543582981</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6113743590194076</v>
+        <v>0.5726978314156028</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3980369775802828</v>
+        <v>0.280948624334961</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6075276843651309</v>
+        <v>0.512821446783704</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4658544565190326</v>
+        <v>-0.5883603815725991</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1405966751107144</v>
+        <v>-0.2135860815196082</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4024177636371959</v>
+        <v>-0.4782197332131943</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.02113776307324144</v>
+        <v>-0.07714785310699313</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2872481247242291</v>
+        <v>-0.34114957067451</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4192182031053662</v>
+        <v>-0.47340289964297</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.008534745980938396</v>
+        <v>-0.03633420845628876</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.4356950551640821</v>
+        <v>-0.4604726817414075</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7532818059133888</v>
+        <v>-0.7760567854283167</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5788282069689075</v>
+        <v>-0.5496584853719497</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001995</t>
+          <t>X &gt; 0.001997</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.950169013453916</v>
+        <v>0.8544288421697743</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4853626651342182</v>
+        <v>0.4415267716423656</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2987988345710306</v>
+        <v>0.164816284790497</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5787217879965922</v>
+        <v>0.4702415781994489</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3387944728282193</v>
+        <v>-0.4871175686038498</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1857991823431178</v>
+        <v>-0.2728458005163432</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.356200086220305</v>
+        <v>-0.4505293912046469</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3276889108417649</v>
+        <v>0.2539128630404406</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2633285813700539</v>
+        <v>-0.3361311698715639</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5243192269343098</v>
+        <v>-0.6006153237573457</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.03658621080079172</v>
+        <v>-0.01028901795517356</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4590709725329347</v>
+        <v>-0.5056972084797735</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7614361956932214</v>
+        <v>-0.8095398926606592</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7123789906963722</v>
+        <v>-0.7039521720058843</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003205</t>
+          <t>X &gt; 0.003206</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.4973600731797276</v>
+        <v>0.389958056314974</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7466075538211712</v>
+        <v>0.6935734239893137</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5306703512959032</v>
+        <v>0.3697166376312779</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.542228039729522</v>
+        <v>1.408056304282709</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5730826824424256</v>
+        <v>-0.758341683629375</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2375076294350293</v>
+        <v>-0.3457937608970951</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3543361757111967</v>
+        <v>-0.4763310520792245</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4140373904117709</v>
+        <v>0.3156978227575564</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.06947997737860589</v>
+        <v>-0.1720329729864858</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3560184920183289</v>
+        <v>-0.4675445244347642</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4251958426792228</v>
+        <v>0.3475680756442827</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.03338375144432604</v>
+        <v>-0.1152794791828313</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4535346047577349</v>
+        <v>-0.5412988428084873</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2982214897424669</v>
+        <v>-0.3231587321525851</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.004415</t>
+          <t>X &gt; 0.004416</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2633428087770326</v>
+        <v>-0.3398280185430735</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7655193169378265</v>
+        <v>0.6646409730957288</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.338776114446446</v>
+        <v>1.189099979772678</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.186975796308964</v>
+        <v>1.986763653708557</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5708405207153007</v>
+        <v>-0.8397142017675705</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2763856916064711</v>
+        <v>0.100850949772564</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4350076368944897</v>
+        <v>-0.627584772174103</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.3594880591001015</v>
+        <v>0.24214173288496</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3743284119727193</v>
+        <v>-0.4626105089730359</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.9719343403463157</v>
+        <v>-1.073678473723653</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5879054733752227</v>
+        <v>-0.6466423175430975</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3012144530636363</v>
+        <v>-0.37465265578588</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5531567277395268</v>
+        <v>-0.6393815894073072</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.084359681381798</v>
+        <v>-1.097912044603866</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.005624</t>
+          <t>X &gt; 0.005625</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.000604560806728216</v>
+        <v>-0.03382099243176384</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.451720474078691</v>
+        <v>1.438850183740094</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.067037696720774</v>
+        <v>1.888104819239928</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.3047272966108</v>
+        <v>1.174996236640069</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5517175788774935</v>
+        <v>-0.789489995987303</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6516407777342437</v>
+        <v>0.4316622246229969</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.7544610840096837</v>
+        <v>-0.9988568783011047</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.6892982976812831</v>
+        <v>0.5374178428750866</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4332549841068811</v>
+        <v>-0.5532955460298794</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.8585453303305854</v>
+        <v>-0.9556278149375856</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.063246488590778</v>
+        <v>-1.207231059199529</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3919256610762218</v>
+        <v>-0.5630476313307611</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.8120765143896307</v>
+        <v>-0.9582055578945869</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.117126426795792</v>
+        <v>-1.178987521885901</v>
       </c>
     </row>
     <row r="26">
@@ -3254,101 +3254,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4442540374928612</v>
+        <v>0.3431490446782348</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>2.971928481261507</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.142554284562316</v>
+        <v>2.985799188598975</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.396421212315637</v>
+        <v>2.16459627329192</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.569542956456381</v>
+        <v>0.3166514801660867</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.900384128190403</v>
+        <v>1.54052395550675</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5232052045631619</v>
+        <v>0.121172214107375</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.110931081324367</v>
+        <v>1.829252497202297</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.228031116582414</v>
+        <v>0.9770624967611496</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9260575257320056</v>
+        <v>0.6967121768157369</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.100561440747363</v>
+        <v>-0.3226456620246978</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.481761917087411</v>
+        <v>0.2196603832372617</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.6095562692534529</v>
+        <v>0.3687201437482699</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1503604126306683</v>
+        <v>0.01404667919595681</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.008043</t>
+          <t>X &gt; 0.008044</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3148510485848988</v>
+        <v>-0.4305458212703428</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.767103652575102</v>
+        <v>2.687904580011413</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.29431998170103</v>
+        <v>2.113334765295257</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.078134243930798</v>
+        <v>0.796564195298366</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8114533443578225</v>
+        <v>-1.139339556865131</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.8569815663199876</v>
+        <v>0.39926874676393</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.03746550432222762</v>
+        <v>-0.5655464744687606</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.863407564095034</v>
+        <v>1.319434508366705</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.073827957663326</v>
+        <v>0.5591345936241154</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9525066112423985</v>
+        <v>0.4586333184149254</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.565656090504973</v>
+        <v>0.07366104447738309</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2357355179058374</v>
+        <v>-0.2298358709606134</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5441821145013535</v>
+        <v>0.09833350808133901</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2234696772961939</v>
+        <v>-0.09356300370101422</v>
       </c>
     </row>
     <row r="28">
@@ -3358,49 +3358,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.127974854063766</v>
+        <v>-2.157170648416397</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.437309641107703</v>
+        <v>1.436122854663047</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4774395460890659</v>
+        <v>-0.6046739571810704</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.583598719374791</v>
+        <v>-2.827731092436984</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.657971093216005</v>
+        <v>-4.96403905691831</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.528680277774157</v>
+        <v>-3.985371185158208</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.063226628444013</v>
+        <v>-2.634262568501313</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1493428912783656</v>
+        <v>-0.7471541524140619</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6865155239916305</v>
+        <v>-1.254714996844982</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.012624796511965</v>
+        <v>-2.549131812954087</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5506592881054857</v>
+        <v>-1.106213436960765</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9924716119406369</v>
+        <v>-1.518634934889981</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.01594896331737772</v>
+        <v>-0.5020281555714519</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.186886815027513</v>
+        <v>-1.536002161480624</v>
       </c>
     </row>
     <row r="29">
@@ -3410,49 +3410,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4559939121542982</v>
+        <v>-0.4851897065069295</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.60571719104356</v>
+        <v>2.604530404598904</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2812660317177134</v>
+        <v>-0.2814194217220347</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.856648364764858</v>
+        <v>-2.020694259012025</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.54384073917717</v>
+        <v>-2.821469879714726</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.654167661810369</v>
+        <v>-4.106316759649687</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.423599168627284</v>
+        <v>-1.051708051367363</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.6866192538320348</v>
+        <v>0.04009158700318949</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.3101796840600457</v>
+        <v>-0.308407501884389</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5397391122698139</v>
+        <v>-1.132236082699372</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.094676448712903</v>
+        <v>1.467361787521554</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.8672249480713745</v>
+        <v>0.279422605883326</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.077988921256392</v>
+        <v>0.507317638821057</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.988267158233711</v>
+        <v>0.4448360210856492</v>
       </c>
     </row>
     <row r="30">
@@ -3462,49 +3462,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.8142493638676811</v>
+        <v>-0.8434451582203124</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.157897876401819</v>
+        <v>2.156711089957163</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.153693565024206</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.310623260162345</v>
+        <v>-3.523809523809533</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.794097581726092</v>
+        <v>-3.179725331428109</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.496723552091005</v>
+        <v>-2.906939812609181</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.3597425592310586</v>
+        <v>-0.05092923516798464</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.153178117124988</v>
+        <v>0.7332380044486797</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5884763083053528</v>
+        <v>-0.9704012713547883</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1778909029545375</v>
+        <v>-0.5442298521697637</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.819088611054177</v>
+        <v>3.41829636696081</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.33245836004815</v>
+        <v>0.9764631043256955</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.752643641188534</v>
+        <v>1.414638511095212</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.558211224188177</v>
+        <v>1.247016706443901</v>
       </c>
     </row>
     <row r="31">
@@ -3514,49 +3514,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.405094332159948</v>
+        <v>1.375898537807316</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.866447099199746</v>
+        <v>1.86526031275509</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.118997860684829</v>
+        <v>-1.11915125068915</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.835815031431522</v>
+        <v>-4.098075499629907</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.811604584527217</v>
+        <v>-3.032920495504115</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.993397221558801</v>
+        <v>-2.242000261659278</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.04689241917503</v>
+        <v>0.8061519392707055</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.142323775388292</v>
+        <v>1.894723323965088</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5228250478011489</v>
+        <v>-0.7329228603012439</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3310771774643442</v>
+        <v>-0.5204820110644164</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.630888330942135</v>
+        <v>3.420455261606747</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5014001833692134</v>
+        <v>-0.6664557212356144</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.6409489633173777</v>
+        <v>0.4927904972782855</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.8666846135439101</v>
+        <v>0.7418353592936526</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.82371973105505</v>
+        <v>1.794523936702419</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4497180176379203</v>
+        <v>-0.450904804082576</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.831244369280377</v>
+        <v>-2.831397759284698</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.025522536950284</v>
+        <v>-4.026017029328287</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.226063745675127</v>
+        <v>-5.177517825909355</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.92868971604004</v>
+        <v>-4.904732307090427</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.702141797160508</v>
+        <v>-1.654130118170187</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.142047837198447</v>
+        <v>1.191295399592164</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.230192597470023</v>
+        <v>-2.156935487690326</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.755608082541606</v>
+        <v>-1.656260757247033</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.33770400423132</v>
+        <v>3.437612040249995</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.925931088446475</v>
+        <v>-1.802234467418231</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.302924680756675</v>
+        <v>0.4516142285345026</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5286603309832074</v>
+        <v>0.7006590905498697</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>123</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.803636814994107</v>
+        <v>2.774441020641476</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.3794425918489708</v>
+        <v>0.378255805404315</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-6.519393833556471</v>
+        <v>-6.519547223560792</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-7.202176820049409</v>
+        <v>-7.202671312427412</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-9.366482633307712</v>
+        <v>-9.31793671354194</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-9.069108603672625</v>
+        <v>-9.045151194723012</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.088778312532284</v>
+        <v>-5.040766633541963</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.303814435993822</v>
+        <v>-2.254566873600105</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.990812852679198</v>
+        <v>-3.917555742899502</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.840731649009058</v>
+        <v>-4.741384323714485</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1673840267814413</v>
+        <v>-0.067475990762766</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.824062784995228</v>
+        <v>-5.700366163966983</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.992181117983428</v>
+        <v>-2.8434915702056</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.392461727919496</v>
+        <v>-4.220462968352834</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.326776277157961</v>
+        <v>2.29758048280533</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.169025200521254</v>
+        <v>-2.17021198696591</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.371488892968607</v>
+        <v>-7.371642282972928</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.164340672457165</v>
+        <v>-9.164835164835168</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-9.702630225552859</v>
+        <v>-9.654084305787087</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-9.405256195917772</v>
+        <v>-9.381298786968159</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-5.643812709030101</v>
+        <v>-5.59580103003978</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.226265968201446</v>
+        <v>-3.177018405807729</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-5.098705382592549</v>
+        <v>-4.999358057297975</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.457252694698887</v>
+        <v>-1.357344658680212</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.153643773112798</v>
+        <v>-8.029947152084553</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.72764078027236</v>
+        <v>-4.578951232494532</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.386520514661221</v>
+        <v>-7.214521755094559</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.735951439345165</v>
+        <v>1.706755644992533</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.534403900498212</v>
+        <v>2.533217114053556</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.884463869799006</v>
+        <v>-3.884617259803328</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.754238726210644</v>
+        <v>-3.754733218588648</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.702166833523201</v>
+        <v>-6.653620913757429</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.199973526779686</v>
+        <v>-5.176016117830073</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-4.07986460893742</v>
+        <v>-4.0318529299471</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.342113975615725</v>
+        <v>-3.292866413222008</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-4.607915409246935</v>
+        <v>-4.534658299467239</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-4.25301492846836</v>
+        <v>-4.153667603173787</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.3615610217051923</v>
+        <v>0.4614690577238676</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.037795765698526</v>
+        <v>-7.914099144670281</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.638669510578197</v>
+        <v>-3.489979962800369</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-5.82257241456854</v>
+        <v>-5.650573655001878</v>
       </c>
     </row>
   </sheetData>
@@ -3904,105 +3904,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01736</t>
+          <t>X &lt; -0.01735</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.81424936386768</v>
+        <v>-10.84344515822031</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.23495926645533</v>
+        <v>-11.23614605289998</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.29639731787703</v>
+        <v>-3.296550707881352</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-7.928076936193428</v>
+        <v>-7.928571428571431</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.323509346431983</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.026135316796896</v>
+        <v>-1.002177907847283</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.301321866539247</v>
+        <v>-2.253310187548927</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.183990442054963</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.273089489202327</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.88881294144452</v>
+        <v>-1.740123393666693</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01615</t>
+          <t>X &lt; -0.01614</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>115</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-7.263524726186525</v>
+        <v>-7.292720520539156</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.135580384467744</v>
+        <v>-7.1367671709124</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.312960464874962</v>
+        <v>-2.313113854879283</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.530561408243116</v>
+        <v>-6.531055900621119</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1123292222083805</v>
+        <v>-0.06378330244260866</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1850448074267064</v>
+        <v>0.2090022163763194</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.7692307692307665</v>
+        <v>-0.7212190902404458</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.111526673939018</v>
+        <v>3.160774236332735</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.180979300024937</v>
+        <v>2.254236409804633</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4080699310875318</v>
+        <v>-0.3087226057929584</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.99592456282619</v>
+        <v>2.095832598844865</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.160737497790208</v>
+        <v>1.284434118818453</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.737674225088419</v>
+        <v>-2.588984677310592</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.511938574861887</v>
+        <v>-2.339939815295224</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>142</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.185141382647025</v>
+        <v>-3.214337176999656</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.387876771485509</v>
+        <v>-3.389063557930164</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2615213956771569</v>
+        <v>-0.2616747856814783</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.948197660539506</v>
+        <v>-2.948692152917509</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.851540955378887</v>
+        <v>2.900086875144659</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.148914985013974</v>
+        <v>3.172872393963587</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.359979273635126</v>
+        <v>2.407990952625447</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.822488094637116</v>
+        <v>6.871735657030833</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.648829881776315</v>
+        <v>4.722086991556012</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.094685733333776</v>
+        <v>3.194033058628349</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.298435279298936</v>
+        <v>4.398343315317611</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.332813431654259</v>
+        <v>4.456510052682503</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3915358177774735</v>
+        <v>0.5402253655553011</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.6172714680040059</v>
+        <v>0.7892702275706682</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>185</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.670105219723538</v>
+        <v>-1.69930101407617</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.119129150625206</v>
+        <v>-1.120315937069861</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.269883248403538</v>
+        <v>2.269729858399216</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2379462298297312</v>
+        <v>0.2374517374517282</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.564521541598907</v>
+        <v>4.613067461364679</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.699733409071833</v>
+        <v>2.723690818021446</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.074482509265124</v>
+        <v>2.122494188255445</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.931738189802708</v>
+        <v>5.980985752196425</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.249134411658311</v>
+        <v>4.322391521438007</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.020837236950072</v>
+        <v>5.120184562244646</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.356676619230427</v>
+        <v>5.456584655249102</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.39105477158575</v>
+        <v>5.514751392613995</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.727660675029092</v>
+        <v>1.87635022280692</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.412855784715084</v>
+        <v>1.584854544281747</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>236</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.06145685082158536</v>
+        <v>0.03226105646895405</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.416372452673002</v>
+        <v>1.415185666228346</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.411431576392538</v>
+        <v>4.411278186388216</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.117927906421585</v>
+        <v>4.117433414043582</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.850824794003849</v>
+        <v>4.899370713769621</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.148198823638936</v>
+        <v>5.172156232588549</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.368573210135487</v>
+        <v>3.416584889125808</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.867606261264001</v>
+        <v>5.916853823657718</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.535437664063252</v>
+        <v>4.608694773842949</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.804162935530009</v>
+        <v>5.903510260824582</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.752004150151173</v>
+        <v>4.851912186169848</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.481297556743783</v>
+        <v>6.604994177772028</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.095045008515115</v>
+        <v>3.243734556292942</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.049594218063689</v>
+        <v>2.221592977630351</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>297</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9657645153828369</v>
+        <v>-0.9949603097354682</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2200482515443127</v>
+        <v>-0.2212350379889685</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.41548339400368</v>
+        <v>2.415330003999358</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.8622068540903669</v>
+        <v>0.8617123617123639</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.670718647796008</v>
+        <v>1.71926456756178</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.978193687532112</v>
+        <v>3.002151096481725</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.230183664966283</v>
+        <v>3.278195343956604</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.120017378081897</v>
+        <v>5.169264940475614</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.712233874757771</v>
+        <v>3.785490984537468</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.882517098629933</v>
+        <v>4.981864423924506</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.994314256868051</v>
+        <v>3.094222292886727</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.375493756024731</v>
+        <v>4.499190377052976</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.271841219209634</v>
+        <v>2.420530766987461</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.160876532735834</v>
+        <v>2.332875292302496</v>
       </c>
     </row>
     <row r="12">
@@ -4223,722 +4223,722 @@
         <v>376</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.88517134968329</v>
+        <v>-0.9143671440359213</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.432527655513077</v>
+        <v>-1.433714441957733</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.03440308739146047</v>
+        <v>0.03424969738713912</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6332441094457053</v>
+        <v>-0.6337386018237083</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.1715336625414</v>
+        <v>-1.122987742775628</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.519457388370284</v>
+        <v>1.543414797319898</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.966661922721137</v>
+        <v>2.014673601711458</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.627252853402474</v>
+        <v>3.676500415796191</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.502440909645664</v>
+        <v>2.57569801942536</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.514224240975373</v>
+        <v>3.613571566269947</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.979735848672632</v>
+        <v>2.079643884691308</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.81198634145349</v>
+        <v>2.935682962481735</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.7960908072890192</v>
+        <v>0.9447803550668468</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.021826457515552</v>
+        <v>1.193825217082214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.00889</t>
+          <t>X &lt; -0.008888</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>461</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4201785034193861</v>
+        <v>-0.4493742977720174</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.380605377394282</v>
+        <v>-1.381792163838938</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8276601142064379</v>
+        <v>0.8275067242021166</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.09020629900954447</v>
+        <v>0.08971180663154144</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6650029937824584</v>
+        <v>-0.6164570740166866</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.150809213726809</v>
+        <v>1.174766622676422</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.933777813245896</v>
+        <v>1.981789492236217</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.852826306118587</v>
+        <v>3.902073868512304</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.791844149595811</v>
+        <v>3.865101259375507</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.809604312051206</v>
+        <v>3.90895163734578</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.303384715613142</v>
+        <v>2.403292751631817</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.988522087057397</v>
+        <v>3.112218708085642</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.049933055869801</v>
+        <v>1.198622603647628</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.275668706096333</v>
+        <v>1.447667465662995</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.007681</t>
+          <t>X &lt; -0.007679</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>580</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.101605685706765</v>
+        <v>-1.130801480059397</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.505895227046459</v>
+        <v>-1.507082013491114</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1682989054398902</v>
+        <v>0.1681455154355689</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.4709378421316899</v>
+        <v>0.4704433497536868</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2397655040674422</v>
+        <v>-0.1912195843016704</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.609332663498677</v>
+        <v>1.63329007244829</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.869449890439405</v>
+        <v>1.917461569429726</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.12651917768715</v>
+        <v>3.175766740080867</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.065537021164374</v>
+        <v>3.138794130944071</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.183330859677767</v>
+        <v>2.283238895696442</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.562536598239987</v>
+        <v>2.686233219268232</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.625144365616237</v>
+        <v>1.773833913394064</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.850880015842769</v>
+        <v>2.022878775409431</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.006471</t>
+          <t>X &lt; -0.006469</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>733</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.867000614436122</v>
+        <v>-1.896196408788754</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.431801987172527</v>
+        <v>-1.432988773617183</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3258912436874652</v>
+        <v>-0.3260446336917866</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.05924045207726891</v>
+        <v>-0.05973494445527194</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3246787091293086</v>
+        <v>-0.2761327893635368</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2455466165494258</v>
+        <v>0.2695040254990388</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.115815793436063</v>
+        <v>1.163827472426384</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.831557517998576</v>
+        <v>2.880805080392292</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.634149713453965</v>
+        <v>2.707406823233661</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.148487397342393</v>
+        <v>3.247834722636966</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.26165799897305</v>
+        <v>2.361566034991725</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.387441335503006</v>
+        <v>3.51113795653125</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.285162242080453</v>
+        <v>2.433851789858281</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.056600484394302</v>
+        <v>3.228599243960964</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.005262</t>
+          <t>X &lt; -0.00526</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>943</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.367448374118659</v>
+        <v>-1.39664416847129</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.236322696238688</v>
+        <v>-2.237509482683343</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.040426000399876</v>
+        <v>-1.040579390404197</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.122289934224028</v>
+        <v>-1.122784426602031</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.130356793788444</v>
+        <v>-1.081810874022672</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1214180842029506</v>
+        <v>0.1453754931525637</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.03670772493678243</v>
+        <v>0.08471940392710309</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.79657439398143</v>
+        <v>1.845821956375147</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.583948547108712</v>
+        <v>2.657205656888408</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.840074289485102</v>
+        <v>1.939421614779675</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8930613602811164</v>
+        <v>0.9929693962997916</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.51810759323029</v>
+        <v>2.641804214258535</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.673778585091853</v>
+        <v>1.82246813286968</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.747870544968443</v>
+        <v>2.919869304535105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.004052</t>
+          <t>X &lt; -0.00405</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2217866721683421</v>
+        <v>0.2278831203531126</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.389399420895487</v>
+        <v>-1.35529396480274</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.8551167515964622</v>
+        <v>-0.7770774885767651</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.062729445845946</v>
+        <v>-1.023809523809526</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.5875054854281174</v>
+        <v>-0.5004004369133384</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2056719963335709</v>
+        <v>-0.1432267324404108</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.131914941697552</v>
+        <v>0.1799266206878727</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5094408925054097</v>
+        <v>0.5586884548991264</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.124134411658311</v>
+        <v>1.197391521438007</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.9498912910041213</v>
+        <v>1.049238616298695</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4073522949061044</v>
+        <v>0.5072603309247796</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.201865582396557</v>
+        <v>1.325562203424802</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5283363507047696</v>
+        <v>0.6770258984825972</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.767585514444811</v>
+        <v>1.939584274011473</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.002843</t>
+          <t>X &lt; -0.002841</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.100745860583132</v>
+        <v>1.099609404562621</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1342589079204402</v>
+        <v>0.1597489741601663</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2409201879218514</v>
+        <v>0.305533902786955</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3451870467132778</v>
+        <v>-0.3127620411085061</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1193887297039211</v>
+        <v>0.2001362767799506</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.918195424095444</v>
+        <v>0.9739955250190633</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.191651253941032</v>
+        <v>1.239662932931353</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.297648512733083</v>
+        <v>1.3468960751268</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.635553088399561</v>
+        <v>1.66808965510176</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.75898140694504</v>
+        <v>1.775493165977316</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.19560019129603</v>
+        <v>1.213186529329484</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.917315418449405</v>
+        <v>1.916052407095513</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.664160956176389</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.554903004348503</v>
+        <v>2.557904958592907</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001633</t>
+          <t>X &lt; -0.001632</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1201412121324168</v>
+        <v>-0.06593560279887356</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7022716151235997</v>
+        <v>-0.6512599245355872</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3706507480626655</v>
+        <v>-0.2876311279648007</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7852197933362888</v>
+        <v>-0.7295733287269002</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05232290575401777</v>
+        <v>0.05082686526677094</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.6082472497890592</v>
+        <v>0.659303381583193</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6446022658255544</v>
+        <v>0.692613944815875</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.7223278109008007</v>
+        <v>0.7715753732945174</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8768948189462833</v>
+        <v>0.9162008271117159</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5458167619295935</v>
+        <v>0.5766337475073939</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.341115603669401</v>
+        <v>0.3724932999713033</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.773678146931978</v>
+        <v>0.7938561632441861</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.176952199563338</v>
+        <v>1.185623176147665</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.619948122954959</v>
+        <v>1.616266101117034</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0004236</t>
+          <t>X &lt; -0.0004221</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1922</v>
+        <v>1929</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.04315669443476366</v>
+        <v>0.04802770999673811</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.253927849739263</v>
+        <v>-0.215315797323079</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1300270353241757</v>
+        <v>-0.01211743120802566</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.82967741040801</v>
+        <v>-0.7339544513457525</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2399168539236811</v>
+        <v>0.3813512731267465</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.381689223807733</v>
+        <v>0.4238041887717898</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5044477442096138</v>
+        <v>0.5470845817577512</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.400449639841959</v>
+        <v>0.4209000054854855</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.575871112032786</v>
+        <v>0.591288723461183</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3260489907599506</v>
+        <v>0.3377037922055592</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1506394131932183</v>
+        <v>0.1335633446694686</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4742148547458243</v>
+        <v>0.5027720727030953</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8115807885903905</v>
+        <v>0.8333787910330059</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.067213576429793</v>
+        <v>1.030583321270242</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.000786</t>
+          <t>X &lt; 0.0007873</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2223</v>
+        <v>2229</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3947787492422989</v>
+        <v>-0.3186985869621211</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4806171527592369</v>
+        <v>-0.4467564715640933</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3818936967785262</v>
+        <v>-0.27932770408718</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5208475572278459</v>
+        <v>-0.4386475593372126</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4213474118837226</v>
+        <v>0.5299520879267234</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1803634334434392</v>
+        <v>0.2448605758563716</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.454558412894194</v>
+        <v>0.5226881041444287</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1220792711262959</v>
+        <v>0.1713268335200127</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4000878785902344</v>
+        <v>0.4483963957605113</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.5181126893220664</v>
+        <v>0.5666943290774284</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1591340631972926</v>
+        <v>0.1831012121828834</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.5334780937843462</v>
+        <v>0.5553101209250642</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.81331107362913</v>
+        <v>0.8330997044554564</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.6600381897922176</v>
+        <v>0.6335128930746805</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001995</t>
+          <t>X &lt; 0.001997</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2475</v>
+        <v>2481</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6872844303731256</v>
+        <v>-0.6210443007712314</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2831541187614306</v>
+        <v>-0.2533210773126413</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2345558944878476</v>
+        <v>-0.1426986602239992</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3864750475540575</v>
+        <v>-0.3128772635814911</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.2441189140620637</v>
+        <v>0.3468447168810656</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1787359908555501</v>
+        <v>0.2391200611993796</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3358636001504465</v>
+        <v>0.4019985112730637</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1312050436362924</v>
+        <v>-0.08195748124257562</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3138685005859543</v>
+        <v>0.3647458467427569</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4948186810807655</v>
+        <v>0.5485754682655397</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1111647635490698</v>
+        <v>0.1429033802618989</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.4509026695442628</v>
+        <v>0.4832144142813632</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6594600026280943</v>
+        <v>0.6926514091201952</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6255229973822978</v>
+        <v>0.6192456463874763</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003205</t>
+          <t>X &lt; 0.003206</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2753</v>
+        <v>2759</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2880925437637885</v>
+        <v>-0.2324545580757018</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3407429354865457</v>
+        <v>-0.3139037382525984</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3005741245184979</v>
+        <v>-0.2178517898191927</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7865142582045053</v>
+        <v>-0.7197921513882477</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3062219226613792</v>
+        <v>0.4034269736648071</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1686557565733722</v>
+        <v>0.2253793954072307</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.2651704788584937</v>
+        <v>0.3295055474407107</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1294081323077236</v>
+        <v>-0.08016056991400689</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1558823488630949</v>
+        <v>0.209071967741508</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3053709545632231</v>
+        <v>0.3638588273034742</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.09658506044635828</v>
+        <v>-0.0577517180941669</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1396690846283732</v>
+        <v>0.1816401008220083</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3572706771881116</v>
+        <v>0.402647451532566</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2767978233756168</v>
+        <v>0.2892421504453537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.004415</t>
+          <t>X &lt; 0.004416</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2984</v>
+        <v>2991</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.07675698852281698</v>
+        <v>0.1074273548395936</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2639510035714352</v>
+        <v>-0.2240427459334313</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5584214856183465</v>
+        <v>-0.4997062443702163</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8628335870985211</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2371249373718172</v>
+        <v>0.3455946463125628</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.06730644924184759</v>
+        <v>0.002211823997363638</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2491868023244734</v>
+        <v>0.3273144445290939</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.06573085114459332</v>
+        <v>-0.01988142514134239</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.259731827407947</v>
+        <v>0.2958976253352859</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4993277756815786</v>
+        <v>0.5419453400736316</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.3470402671099748</v>
+        <v>0.3712385267735812</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2329294661061141</v>
+        <v>0.2622370929582587</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.334206919766288</v>
+        <v>0.3685836799350639</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.5455273302552683</v>
+        <v>0.5507612734783507</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.005624</t>
+          <t>X &lt; 0.005625</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3231</v>
+        <v>3238</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.02645477706105481</v>
+        <v>-0.01626946035496957</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3861107709113369</v>
+        <v>-0.3821709550074246</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6264658493044308</v>
+        <v>-0.5745191965707264</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.372707660626503</v>
+        <v>-0.3355712084525706</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1699169308114676</v>
+        <v>0.2399211954933875</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1503742650012541</v>
+        <v>-0.08701998528881205</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.2899308173632136</v>
+        <v>0.3626529157676543</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1292625699932373</v>
+        <v>-0.08621072536721641</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.2284883020134387</v>
+        <v>0.2641666298797816</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.3539756303666763</v>
+        <v>0.3836542684435855</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4140902480726254</v>
+        <v>0.4573773590365491</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2185516157853442</v>
+        <v>0.2685542847311737</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3418565540764575</v>
+        <v>0.3849391081715865</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4304806519221245</v>
+        <v>0.4486844025526153</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3443</v>
+        <v>3450</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.119281721638373</v>
+        <v>-0.09751430971795827</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.6138412540329625</v>
+        <v>-0.5961790834532437</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6897720590778533</v>
+        <v>-0.6564400235382308</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5015759009967411</v>
+        <v>-0.4531521110468546</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1123292222083805</v>
+        <v>-0.05900408950351022</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3656798302544502</v>
+        <v>-0.2911990718684478</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.04459308807133766</v>
+        <v>0.04012238084744979</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3798444859434937</v>
+        <v>-0.3230252651903882</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1639213355041633</v>
+        <v>-0.1124516623191667</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.09853801297348497</v>
+        <v>-0.05127890585845307</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1192685785722389</v>
+        <v>0.1664611501154525</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.004151755696256032</v>
+        <v>0.05076523897265872</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.03050864411583376</v>
+        <v>0.01971097486332241</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.06644983767015589</v>
+        <v>0.09484279340043145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.008043</t>
+          <t>X &lt; 0.008044</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3624</v>
+        <v>3632</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.02459057739516624</v>
+        <v>0.04202868005264548</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3878884083682195</v>
+        <v>-0.3738269281597724</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3695504568522523</v>
+        <v>-0.3409533124157491</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1567034460097005</v>
+        <v>-0.1138031153136936</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1312256734366102</v>
+        <v>0.181080529377752</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.09467212287156457</v>
+        <v>-0.02565374500819217</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.0684831196248652</v>
+        <v>0.1485851500253474</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.218213414694354</v>
+        <v>-0.1372138331464114</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.0711682552963282</v>
+        <v>0.005946363408682487</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.05142355747170058</v>
+        <v>0.02259729134238597</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.007456431300553845</v>
+        <v>0.08152329779917977</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.05735372359898605</v>
+        <v>0.1276466991509153</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.01135126216795612</v>
+        <v>0.07836832019946627</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.05956540824589496</v>
+        <v>0.1071488650342118</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3753</v>
+        <v>3760</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.2178343018240625</v>
+        <v>0.2205350467991209</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1293361661513686</v>
+        <v>-0.1288232510664358</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.03440308739146047</v>
+        <v>0.04878212021009887</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2976069543840794</v>
+        <v>0.3257969146799056</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.5305939970330726</v>
+        <v>0.5676207407587199</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4290318564553814</v>
+        <v>0.4834681158927125</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2911300078275119</v>
+        <v>0.3577714198152009</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.07811121885730188</v>
+        <v>0.1455886020582327</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.164874526440471</v>
+        <v>0.2295633053366828</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3145232572796957</v>
+        <v>0.3771316501776525</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1514554235938874</v>
+        <v>0.2145483605812259</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2008579169414872</v>
+        <v>0.261117008429224</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.08876018690111209</v>
+        <v>0.146908014641312</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2230328682734637</v>
+        <v>0.262974153252415</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3856</v>
+        <v>3863</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.01584981681364184</v>
+        <v>0.01826794807483623</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1842346287741705</v>
+        <v>-0.1836114906879942</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.004454475079349152</v>
+        <v>0.004454774332181444</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1605662352869217</v>
+        <v>0.1742281730662825</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2176688644329943</v>
+        <v>0.2414179192605843</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.333836577733635</v>
+        <v>0.3734356287065808</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.09380651875221702</v>
+        <v>0.1460991886046301</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.003427693910651897</v>
+        <v>0.05627582645263374</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.0603302228541196</v>
+        <v>0.1111223411926048</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1314660004285813</v>
+        <v>0.1808154025496478</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.08458739679389282</v>
+        <v>-0.03466966166482166</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.0161931292279931</v>
+        <v>0.06389303101823884</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.0004713979305677185</v>
+        <v>0.04559089204758493</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.006553216586787869</v>
+        <v>0.05040785322102437</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3935</v>
+        <v>3944</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.0279537109760355</v>
+        <v>0.02969105608345046</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.09970668633582846</v>
+        <v>-0.09935564411765796</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.05166604539932251</v>
+        <v>0.05153188798885111</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.2072461585617162</v>
+        <v>0.2205000361297778</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.1760559969467437</v>
+        <v>0.2004079007162503</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1830600022132884</v>
+        <v>0.2087821846917564</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.03614279969254142</v>
+        <v>0.06075135202513593</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.01105311710938395</v>
+        <v>0.01382872174825422</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1196241907775288</v>
+        <v>0.1427497373394004</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.09614102512514933</v>
+        <v>0.1181308367866691</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1450872065557505</v>
+        <v>-0.122472993735073</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.005145621389068822</v>
+        <v>0.02592247246221291</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.01962014237368237</v>
+        <v>-0.0001270148870489152</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.008209499120219732</v>
+        <v>0.009694191230927629</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3981</v>
+        <v>3991</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.08923058099766479</v>
+        <v>-0.087534402309565</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.05903599133365134</v>
+        <v>-0.0588147656511282</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.03580251269413282</v>
+        <v>0.03571173232710834</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1910840331304087</v>
+        <v>0.2042168029421134</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1426560671018535</v>
+        <v>0.1536080019052264</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1279312233313092</v>
+        <v>0.1400719403290509</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.006792954113180372</v>
+        <v>0.01806359458023366</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.04525460434584261</v>
+        <v>-0.03379560409105409</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1082901052344738</v>
+        <v>0.1181873172337973</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1003584143382525</v>
+        <v>0.1091910906754521</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.09024620721047683</v>
+        <v>-0.08091077708860439</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1088757811466436</v>
+        <v>0.1165207051271011</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.05445557640963017</v>
+        <v>0.06109809693355572</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.04324201118269855</v>
+        <v>0.04869548369271826</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4022</v>
+        <v>4033</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0893423006706584</v>
+        <v>-0.0879664961672546</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.04770947779001489</v>
+        <v>0.04762579947509238</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.08788473612979431</v>
+        <v>0.08765163774533136</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1572405241240276</v>
+        <v>0.1568319140666361</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2030526551982419</v>
+        <v>0.2006144343643967</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.21633189341226</v>
+        <v>0.2148122289646892</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1204063184056068</v>
+        <v>0.1182126790234435</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.01451013752004116</v>
+        <v>0.01255631756248476</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1658855307933393</v>
+        <v>0.1625853556883072</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1493935130473361</v>
+        <v>0.1451228024417404</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.04134251791915489</v>
+        <v>-0.04511625279472753</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1561130704412577</v>
+        <v>0.1508745045735296</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.07312022854232936</v>
+        <v>0.06713396639185021</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.06432674846850261</v>
+        <v>0.05745558569012132</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4050</v>
+        <v>4061</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1058237342015929</v>
+        <v>-0.1046135431000366</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01917311027675339</v>
+        <v>0.01915891711159645</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1794648319570555</v>
+        <v>0.1789848894617165</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.224632423412487</v>
+        <v>0.2240411271361893</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2910684876580518</v>
+        <v>0.2887431370403561</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3063296553920765</v>
+        <v>0.3047420092962767</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2105036672236764</v>
+        <v>0.208411964438703</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.126791231009598</v>
+        <v>0.1248862300039661</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2027452357993482</v>
+        <v>0.1998725440247853</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2298400236538924</v>
+        <v>0.2260653507822639</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.08837352709313251</v>
+        <v>0.08496303362747426</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2600550650677818</v>
+        <v>0.255423642515872</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1747574879615073</v>
+        <v>0.1695621940100338</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2169932555192275</v>
+        <v>0.2109418480346505</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4069</v>
+        <v>4080</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0801321010880045</v>
+        <v>-0.07913210341129684</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.08579545052580784</v>
+        <v>0.08559672045569044</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1699892367448115</v>
+        <v>0.1695362891271799</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2400665163334494</v>
+        <v>0.2394341599720491</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2546452111242417</v>
+        <v>0.2526542234752895</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2712121726035761</v>
+        <v>0.2698377477300156</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1999632402414449</v>
+        <v>0.1981328315476247</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1390006670038346</v>
+        <v>0.137300657410016</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.214319036636752</v>
+        <v>0.2117692712808719</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.212773587737388</v>
+        <v>0.2095246368932422</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1201237598877753</v>
+        <v>0.1171085148912567</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2911722803989036</v>
+        <v>0.2870543177831522</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2043191516875709</v>
+        <v>0.1997606216890162</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2719950911387272</v>
+        <v>0.2666245495811594</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4088</v>
+        <v>4099</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.05467852748631685</v>
+        <v>-0.05388614395312885</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.005458852011578585</v>
+        <v>0.005470515887594729</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.0874129029666193</v>
+        <v>0.08718234738454811</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1089446074166958</v>
+        <v>0.1086639084935399</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1453354528985429</v>
+        <v>0.1438709035605257</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1143501742745343</v>
+        <v>0.1135130727085709</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1162605510431689</v>
+        <v>0.1148850203929825</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1022447980230439</v>
+        <v>0.1008790925526242</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1524895136452216</v>
+        <v>0.1504564284502763</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1469897824574531</v>
+        <v>0.1443922942271811</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.05380346986497386</v>
+        <v>0.05144279959529285</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2242008761254937</v>
+        <v>0.2208547161277039</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1357826634885697</v>
+        <v>0.1321181858919473</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1797146200670738</v>
+        <v>0.1754138764853863</v>
       </c>
     </row>
   </sheetData>
